--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5055,6 +5055,166 @@
         <v>180200</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>009816</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>凱基台灣TOP50</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G116" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H116" t="n">
+        <v>215</v>
+      </c>
+      <c r="I116" t="n">
+        <v>151</v>
+      </c>
+      <c r="J116" t="n">
+        <v>150834</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>009816</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>凱基台灣TOP50</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>62</v>
+      </c>
+      <c r="G117" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="H117" t="n">
+        <v>20</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>主動統一台股增長</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G118" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="H118" t="n">
+        <v>207</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>-146087</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>主動統一台股增長</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>283</v>
+      </c>
+      <c r="G119" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="H119" t="n">
+        <v>20</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>-5915</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5215,6 +5215,166 @@
         <v>-5915</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G120" t="n">
+        <v>188</v>
+      </c>
+      <c r="H120" t="n">
+        <v>267</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>-188267</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G121" t="n">
+        <v>183</v>
+      </c>
+      <c r="H121" t="n">
+        <v>260</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>-183260</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>00713</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>元大台灣高息低波</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>爸爸合資</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>195</v>
+      </c>
+      <c r="G122" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="H122" t="n">
+        <v>20</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>-10053</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>00757</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>統一FANG+</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>48</v>
+      </c>
+      <c r="G123" t="n">
+        <v>104.65</v>
+      </c>
+      <c r="H123" t="n">
+        <v>20</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>-5043</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5375,6 +5375,86 @@
         <v>-5043</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>00631L</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>元大台灣50正2</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>250</v>
+      </c>
+      <c r="G124" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="H124" t="n">
+        <v>20</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>-5030</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>00757</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>統一FANG+</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>48</v>
+      </c>
+      <c r="G125" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="H125" t="n">
+        <v>20</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>-5031</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J125"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5455,6 +5455,166 @@
         <v>-5031</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>00631L</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>元大台灣50正2</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>212</v>
+      </c>
+      <c r="G126" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="H126" t="n">
+        <v>20</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-5038</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>00757</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>統一FANG+</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>45</v>
+      </c>
+      <c r="G127" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="H127" t="n">
+        <v>20</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-5024</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>009816</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>凱基台灣TOP50</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>93</v>
+      </c>
+      <c r="G128" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>-972</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>主動統一台股增長</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>48</v>
+      </c>
+      <c r="G129" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>-979</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交易記錄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="交易記錄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5615,6 +5615,166 @@
         <v>-979</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G130" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="H130" t="n">
+        <v>146</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-102946</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G131" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="H131" t="n">
+        <v>154</v>
+      </c>
+      <c r="I131" t="n">
+        <v>325</v>
+      </c>
+      <c r="J131" t="n">
+        <v>107921</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G132" t="n">
+        <v>224.5</v>
+      </c>
+      <c r="H132" t="n">
+        <v>639</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1347</v>
+      </c>
+      <c r="J132" t="n">
+        <v>447014</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>6206</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>飛捷</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G133" t="n">
+        <v>103</v>
+      </c>
+      <c r="H133" t="n">
+        <v>146</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>-103146</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="交易記錄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交易記錄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1737,16 +1737,16 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45246</v>
+        <v>45215</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>00878</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>475</v>
+        <v>205</v>
       </c>
       <c r="G33" t="n">
-        <v>20.29</v>
+        <v>47.18</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
@@ -1772,21 +1772,21 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-9639</v>
+        <v>-9673</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45278</v>
+        <v>45246</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>00878</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>459</v>
+        <v>200</v>
       </c>
       <c r="G34" t="n">
-        <v>21.02</v>
+        <v>48.4</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -1812,12 +1812,12 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-9649</v>
+        <v>-9681</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45307</v>
+        <v>45246</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="G35" t="n">
-        <v>21.09</v>
+        <v>20.29</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
@@ -1852,21 +1852,21 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-9597</v>
+        <v>-9639</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45338</v>
+        <v>45278</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>00878</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>433</v>
+        <v>194</v>
       </c>
       <c r="G36" t="n">
-        <v>22.32</v>
+        <v>50.44</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
@@ -1892,12 +1892,12 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-9666</v>
+        <v>-9786</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45349</v>
+        <v>45278</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>668</v>
+        <v>459</v>
       </c>
       <c r="G37" t="n">
-        <v>21.89</v>
+        <v>21.02</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
@@ -1932,21 +1932,21 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-14624</v>
+        <v>-9649</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45863</v>
+        <v>45307</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00878</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1960,33 +1960,33 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>95</v>
+        <v>455</v>
       </c>
       <c r="G38" t="n">
-        <v>105.8</v>
+        <v>21.09</v>
       </c>
       <c r="H38" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-10071</v>
+        <v>-9597</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45870</v>
+        <v>45307</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2000,33 +2000,33 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>47</v>
+        <v>194</v>
       </c>
       <c r="G39" t="n">
-        <v>108.25</v>
+        <v>49.48</v>
       </c>
       <c r="H39" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-5108</v>
+        <v>-9600</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45877</v>
+        <v>45338</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00878</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2040,33 +2040,33 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>47</v>
+        <v>433</v>
       </c>
       <c r="G40" t="n">
-        <v>108.1</v>
+        <v>22.32</v>
       </c>
       <c r="H40" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-5101</v>
+        <v>-9666</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45888</v>
+        <v>45338</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2080,33 +2080,33 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>46</v>
+        <v>193</v>
       </c>
       <c r="G41" t="n">
-        <v>110.3</v>
+        <v>50.46</v>
       </c>
       <c r="H41" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-5094</v>
+        <v>-9740</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45891</v>
+        <v>45349</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00878</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2120,33 +2120,33 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>46</v>
+        <v>668</v>
       </c>
       <c r="G42" t="n">
-        <v>108.6</v>
+        <v>21.89</v>
       </c>
       <c r="H42" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>-5016</v>
+        <v>-14624</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45898</v>
+        <v>45398</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2160,33 +2160,33 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="G43" t="n">
-        <v>112.85</v>
+        <v>53.9</v>
       </c>
       <c r="H43" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>-4985</v>
+        <v>-53976</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45905</v>
+        <v>45408</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2200,33 +2200,33 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>43</v>
+        <v>176</v>
       </c>
       <c r="G44" t="n">
-        <v>114.2</v>
+        <v>55.36</v>
       </c>
       <c r="H44" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>-4931</v>
+        <v>-9744</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45912</v>
+        <v>45439</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2240,24 +2240,24 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>43</v>
+        <v>171</v>
       </c>
       <c r="G45" t="n">
-        <v>114.9</v>
+        <v>58.16</v>
       </c>
       <c r="H45" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>-4961</v>
+        <v>-9946</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45919</v>
+        <v>45863</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="G46" t="n">
-        <v>117.55</v>
+        <v>105.8</v>
       </c>
       <c r="H46" t="n">
         <v>20</v>
@@ -2292,12 +2292,12 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>-4957</v>
+        <v>-10071</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45926</v>
+        <v>45870</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G47" t="n">
-        <v>117.55</v>
+        <v>108.25</v>
       </c>
       <c r="H47" t="n">
         <v>20</v>
@@ -2332,26 +2332,26 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>-5075</v>
+        <v>-5108</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45933</v>
+        <v>45873</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>43</v>
+        <v>197</v>
       </c>
       <c r="G48" t="n">
-        <v>117.35</v>
+        <v>51</v>
       </c>
       <c r="H48" t="n">
         <v>20</v>
@@ -2372,12 +2372,12 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>-5066</v>
+        <v>-10067</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45939</v>
+        <v>45877</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G49" t="n">
-        <v>118.6</v>
+        <v>108.1</v>
       </c>
       <c r="H49" t="n">
         <v>20</v>
@@ -2412,12 +2412,12 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>-5001</v>
+        <v>-5101</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45947</v>
+        <v>45888</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G50" t="n">
-        <v>116.1</v>
+        <v>110.3</v>
       </c>
       <c r="H50" t="n">
         <v>20</v>
@@ -2452,12 +2452,12 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>-5012</v>
+        <v>-5094</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45953</v>
+        <v>45891</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G51" t="n">
-        <v>118.7</v>
+        <v>108.6</v>
       </c>
       <c r="H51" t="n">
         <v>20</v>
@@ -2492,26 +2492,26 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>-5005</v>
+        <v>-5016</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45961</v>
+        <v>45898</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>40</v>
+        <v>195</v>
       </c>
       <c r="G52" t="n">
-        <v>125.4</v>
+        <v>51.25</v>
       </c>
       <c r="H52" t="n">
         <v>20</v>
@@ -2532,12 +2532,12 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>-5036</v>
+        <v>-10014</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45968</v>
+        <v>45898</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G53" t="n">
-        <v>121.1</v>
+        <v>112.85</v>
       </c>
       <c r="H53" t="n">
         <v>20</v>
@@ -2572,12 +2572,12 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>-5106</v>
+        <v>-4985</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45975</v>
+        <v>45905</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G54" t="n">
-        <v>120.7</v>
+        <v>114.2</v>
       </c>
       <c r="H54" t="n">
         <v>20</v>
@@ -2612,12 +2612,12 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>-5089</v>
+        <v>-4931</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45982</v>
+        <v>45912</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>43</v>
       </c>
       <c r="G55" t="n">
-        <v>117.15</v>
+        <v>114.9</v>
       </c>
       <c r="H55" t="n">
         <v>20</v>
@@ -2652,12 +2652,12 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>-5057</v>
+        <v>-4961</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45989</v>
+        <v>45919</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G56" t="n">
-        <v>123.05</v>
+        <v>117.55</v>
       </c>
       <c r="H56" t="n">
         <v>20</v>
@@ -2692,12 +2692,12 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>-5065</v>
+        <v>-4957</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45996</v>
+        <v>45926</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G57" t="n">
-        <v>123.15</v>
+        <v>117.55</v>
       </c>
       <c r="H57" t="n">
         <v>20</v>
@@ -2732,12 +2732,12 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>-5069</v>
+        <v>-5075</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46003</v>
+        <v>45933</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G58" t="n">
-        <v>121.95</v>
+        <v>117.35</v>
       </c>
       <c r="H58" t="n">
         <v>20</v>
@@ -2772,26 +2772,26 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>-5020</v>
+        <v>-5066</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46013</v>
+        <v>45937</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>42</v>
+        <v>195</v>
       </c>
       <c r="G59" t="n">
-        <v>119.45</v>
+        <v>51.35</v>
       </c>
       <c r="H59" t="n">
         <v>20</v>
@@ -2812,12 +2812,12 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>-5037</v>
+        <v>-10033</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46017</v>
+        <v>45939</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>42</v>
       </c>
       <c r="G60" t="n">
-        <v>119.6</v>
+        <v>118.6</v>
       </c>
       <c r="H60" t="n">
         <v>20</v>
@@ -2852,21 +2852,21 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>-5043</v>
+        <v>-5001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46031</v>
+        <v>45947</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="G61" t="n">
-        <v>400.7</v>
+        <v>116.1</v>
       </c>
       <c r="H61" t="n">
         <v>20</v>
@@ -2892,12 +2892,12 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>-6832</v>
+        <v>-5012</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46031</v>
+        <v>45953</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="G62" t="n">
-        <v>117.65</v>
+        <v>118.7</v>
       </c>
       <c r="H62" t="n">
         <v>20</v>
@@ -2932,26 +2932,26 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>-10020</v>
+        <v>-5005</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46035</v>
+        <v>45961</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2960,38 +2960,38 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2000</v>
+        <v>197</v>
       </c>
       <c r="G63" t="n">
-        <v>50.3</v>
+        <v>51.35</v>
       </c>
       <c r="H63" t="n">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>-100743</v>
+        <v>-10136</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46036</v>
+        <v>45961</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3000,33 +3000,33 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2000</v>
+        <v>40</v>
       </c>
       <c r="G64" t="n">
-        <v>54.4</v>
+        <v>125.4</v>
       </c>
       <c r="H64" t="n">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>-108955</v>
+        <v>-5036</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46038</v>
+        <v>45968</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G65" t="n">
-        <v>427.75</v>
+        <v>121.1</v>
       </c>
       <c r="H65" t="n">
         <v>20</v>
@@ -3052,26 +3052,26 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>-6864</v>
+        <v>-5106</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46038</v>
+        <v>45968</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3080,38 +3080,38 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1000</v>
+        <v>195</v>
       </c>
       <c r="G66" t="n">
-        <v>55</v>
+        <v>51.3</v>
       </c>
       <c r="H66" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>-55078</v>
+        <v>-10024</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46041</v>
+        <v>45975</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3120,33 +3120,33 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="G67" t="n">
-        <v>58</v>
+        <v>120.7</v>
       </c>
       <c r="H67" t="n">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>-58082</v>
+        <v>-5089</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46045</v>
+        <v>45982</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G68" t="n">
-        <v>441.7</v>
+        <v>117.15</v>
       </c>
       <c r="H68" t="n">
         <v>20</v>
@@ -3172,26 +3172,26 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>-6646</v>
+        <v>-5057</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46045</v>
+        <v>45989</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3200,38 +3200,38 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1000</v>
+        <v>41</v>
       </c>
       <c r="G69" t="n">
-        <v>58</v>
+        <v>123.05</v>
       </c>
       <c r="H69" t="n">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>-58082</v>
+        <v>-5065</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46045</v>
+        <v>45989</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>44</v>
+        <v>200</v>
       </c>
       <c r="G70" t="n">
-        <v>114.3</v>
+        <v>50.45</v>
       </c>
       <c r="H70" t="n">
         <v>20</v>
@@ -3252,26 +3252,26 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>-5049</v>
+        <v>-10110</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46049</v>
+        <v>45996</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3280,38 +3280,38 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1000</v>
+        <v>41</v>
       </c>
       <c r="G71" t="n">
-        <v>56.5</v>
+        <v>123.15</v>
       </c>
       <c r="H71" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>-56580</v>
+        <v>-5069</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46049</v>
+        <v>46003</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3320,38 +3320,38 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1000</v>
+        <v>41</v>
       </c>
       <c r="G72" t="n">
-        <v>55</v>
+        <v>121.95</v>
       </c>
       <c r="H72" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>-55078</v>
+        <v>-5020</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46051</v>
+        <v>46013</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3360,24 +3360,24 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="G73" t="n">
-        <v>53.7</v>
+        <v>119.45</v>
       </c>
       <c r="H73" t="n">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>-53776</v>
+        <v>-5037</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46052</v>
+        <v>46017</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G74" t="n">
-        <v>114.1</v>
+        <v>119.6</v>
       </c>
       <c r="H74" t="n">
         <v>20</v>
@@ -3412,26 +3412,26 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>-5040</v>
+        <v>-5043</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46052</v>
+        <v>46022</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3440,33 +3440,33 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1000</v>
+        <v>198</v>
       </c>
       <c r="G75" t="n">
-        <v>50.1</v>
+        <v>50.7</v>
       </c>
       <c r="H75" t="n">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>-50171</v>
+        <v>-10059</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46052</v>
+        <v>46031</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="G76" t="n">
-        <v>447.35</v>
+        <v>117.65</v>
       </c>
       <c r="H76" t="n">
         <v>20</v>
@@ -3492,12 +3492,12 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>-6730</v>
+        <v>-10020</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46055</v>
+        <v>46035</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3520,38 +3520,38 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G77" t="n">
-        <v>48.3</v>
+        <v>50.3</v>
       </c>
       <c r="H77" t="n">
-        <v>68</v>
+        <v>143</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>-48368</v>
+        <v>-100743</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46059</v>
+        <v>46036</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3560,24 +3560,24 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>16</v>
+        <v>2000</v>
       </c>
       <c r="G78" t="n">
-        <v>429.35</v>
+        <v>54.4</v>
       </c>
       <c r="H78" t="n">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>-6890</v>
+        <v>-108955</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46062</v>
+        <v>46038</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3603,21 +3603,21 @@
         <v>1000</v>
       </c>
       <c r="G79" t="n">
-        <v>48.15</v>
+        <v>55</v>
       </c>
       <c r="H79" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>-48218</v>
+        <v>-55078</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46062</v>
+        <v>46041</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3643,35 +3643,35 @@
         <v>1000</v>
       </c>
       <c r="G80" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H80" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>-49069</v>
+        <v>-58082</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46064</v>
+        <v>46045</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3680,38 +3680,38 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="G81" t="n">
-        <v>110.35</v>
+        <v>58</v>
       </c>
       <c r="H81" t="n">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>-5096</v>
+        <v>-58082</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46076</v>
+        <v>46045</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3720,38 +3720,38 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="G82" t="n">
-        <v>50</v>
+        <v>114.3</v>
       </c>
       <c r="H82" t="n">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>-50071</v>
+        <v>-5049</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46079</v>
+        <v>46049</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3760,38 +3760,38 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>47</v>
+        <v>1000</v>
       </c>
       <c r="G83" t="n">
-        <v>106.9</v>
+        <v>56.5</v>
       </c>
       <c r="H83" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>-5044</v>
+        <v>-56580</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46079</v>
+        <v>46049</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3800,38 +3800,38 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="G84" t="n">
-        <v>538.05</v>
+        <v>55</v>
       </c>
       <c r="H84" t="n">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>-6477</v>
+        <v>-55078</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46087</v>
+        <v>46051</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3840,33 +3840,33 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>45</v>
+        <v>1000</v>
       </c>
       <c r="G85" t="n">
-        <v>112.45</v>
+        <v>53.7</v>
       </c>
       <c r="H85" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>-5080</v>
+        <v>-53776</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46087</v>
+        <v>46052</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="G86" t="n">
-        <v>478.85</v>
+        <v>114.1</v>
       </c>
       <c r="H86" t="n">
         <v>20</v>
@@ -3892,26 +3892,26 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>-6724</v>
+        <v>-5040</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46092</v>
+        <v>46052</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>009816</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3920,38 +3920,38 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>14000</v>
+        <v>1000</v>
       </c>
       <c r="G87" t="n">
-        <v>10.95</v>
+        <v>50.1</v>
       </c>
       <c r="H87" t="n">
-        <v>218</v>
+        <v>71</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>-153518</v>
+        <v>-50171</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46092</v>
+        <v>46052</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>009816</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3960,10 +3960,10 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>62</v>
+        <v>195</v>
       </c>
       <c r="G88" t="n">
-        <v>10.96</v>
+        <v>51.3</v>
       </c>
       <c r="H88" t="n">
         <v>20</v>
@@ -3972,26 +3972,26 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>-700</v>
+        <v>-10024</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46094</v>
+        <v>46055</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4000,38 +4000,38 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="G89" t="n">
-        <v>465</v>
+        <v>48.3</v>
       </c>
       <c r="H89" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>-5135</v>
+        <v>-48368</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46094</v>
+        <v>46062</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4040,33 +4040,33 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>45</v>
+        <v>1000</v>
       </c>
       <c r="G90" t="n">
-        <v>111.7</v>
+        <v>48.15</v>
       </c>
       <c r="H90" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>-5046</v>
+        <v>-48218</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46099</v>
+        <v>46062</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4080,38 +4080,38 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G91" t="n">
-        <v>35.9</v>
+        <v>49</v>
       </c>
       <c r="H91" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>-71902</v>
+        <v>-49069</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46099</v>
+        <v>46064</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4120,33 +4120,33 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3000</v>
+        <v>46</v>
       </c>
       <c r="G92" t="n">
-        <v>35.95</v>
+        <v>110.35</v>
       </c>
       <c r="H92" t="n">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>-108003</v>
+        <v>-5096</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46100</v>
+        <v>46076</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4160,38 +4160,38 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G93" t="n">
-        <v>33.5</v>
+        <v>50</v>
       </c>
       <c r="H93" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>-67095</v>
+        <v>-50071</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46100</v>
+        <v>46079</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4200,38 +4200,38 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1000</v>
+        <v>186</v>
       </c>
       <c r="G94" t="n">
-        <v>33.3</v>
+        <v>53.85</v>
       </c>
       <c r="H94" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>-33347</v>
+        <v>-10036</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46100</v>
+        <v>46079</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4240,24 +4240,24 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2000</v>
+        <v>47</v>
       </c>
       <c r="G95" t="n">
-        <v>33.55</v>
+        <v>106.9</v>
       </c>
       <c r="H95" t="n">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>-67195</v>
+        <v>-5044</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46101</v>
+        <v>46087</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G96" t="n">
-        <v>109.45</v>
+        <v>112.45</v>
       </c>
       <c r="H96" t="n">
         <v>20</v>
@@ -4292,21 +4292,21 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>-5055</v>
+        <v>-5080</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46101</v>
+        <v>46092</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>009816</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="G97" t="n">
-        <v>469.4</v>
+        <v>10.96</v>
       </c>
       <c r="H97" t="n">
         <v>20</v>
@@ -4332,21 +4332,21 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>-5183</v>
+        <v>-700</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45215</v>
+        <v>46092</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>009816</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4360,33 +4360,33 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>205</v>
+        <v>14000</v>
       </c>
       <c r="G98" t="n">
-        <v>47.18</v>
+        <v>10.95</v>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>218</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>-9673</v>
+        <v>-153518</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45246</v>
+        <v>46094</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4400,38 +4400,38 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="G99" t="n">
-        <v>48.4</v>
+        <v>111.7</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>-9681</v>
+        <v>-5046</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45278</v>
+        <v>46099</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4440,38 +4440,38 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>194</v>
+        <v>2000</v>
       </c>
       <c r="G100" t="n">
-        <v>50.44</v>
+        <v>35.9</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>-9786</v>
+        <v>-71902</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45307</v>
+        <v>46099</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4480,38 +4480,38 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>194</v>
+        <v>3000</v>
       </c>
       <c r="G101" t="n">
-        <v>49.48</v>
+        <v>35.95</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>-9600</v>
+        <v>-108003</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45338</v>
+        <v>46100</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4520,38 +4520,38 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>193</v>
+        <v>2000</v>
       </c>
       <c r="G102" t="n">
-        <v>50.46</v>
+        <v>33.55</v>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>-9740</v>
+        <v>-67195</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45398</v>
+        <v>46100</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4563,35 +4563,35 @@
         <v>1000</v>
       </c>
       <c r="G103" t="n">
-        <v>53.9</v>
+        <v>33.3</v>
       </c>
       <c r="H103" t="n">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>-53976</v>
+        <v>-33347</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45408</v>
+        <v>46100</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4600,33 +4600,33 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>176</v>
+        <v>2000</v>
       </c>
       <c r="G104" t="n">
-        <v>55.36</v>
+        <v>33.5</v>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>-9744</v>
+        <v>-67095</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45439</v>
+        <v>46101</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4640,38 +4640,38 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>171</v>
+        <v>46</v>
       </c>
       <c r="G105" t="n">
-        <v>58.16</v>
+        <v>109.45</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>-9946</v>
+        <v>-5055</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45873</v>
+        <v>46106</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>主動統一台股增長</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4680,78 +4680,78 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>197</v>
+        <v>7000</v>
       </c>
       <c r="G106" t="n">
-        <v>51</v>
+        <v>20.84</v>
       </c>
       <c r="H106" t="n">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>-10067</v>
+        <v>-146087</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45898</v>
+        <v>46106</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>009816</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>195</v>
+        <v>14000</v>
       </c>
       <c r="G107" t="n">
-        <v>51.25</v>
+        <v>10.8</v>
       </c>
       <c r="H107" t="n">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="J107" t="n">
-        <v>-10014</v>
+        <v>150834</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45937</v>
+        <v>46106</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>主動統一台股增長</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4760,10 +4760,10 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>195</v>
+        <v>283</v>
       </c>
       <c r="G108" t="n">
-        <v>51.35</v>
+        <v>20.83</v>
       </c>
       <c r="H108" t="n">
         <v>20</v>
@@ -4772,38 +4772,38 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>-10033</v>
+        <v>-5915</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45961</v>
+        <v>46106</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>009816</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>197</v>
+        <v>62</v>
       </c>
       <c r="G109" t="n">
-        <v>51.35</v>
+        <v>10.78</v>
       </c>
       <c r="H109" t="n">
         <v>20</v>
@@ -4812,66 +4812,66 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>-10136</v>
+        <v>648</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>45968</v>
+        <v>46106</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>195</v>
+        <v>5000</v>
       </c>
       <c r="G110" t="n">
-        <v>51.3</v>
+        <v>36.2</v>
       </c>
       <c r="H110" t="n">
-        <v>20</v>
+        <v>257</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>543</v>
       </c>
       <c r="J110" t="n">
-        <v>-10024</v>
+        <v>180200</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>45989</v>
+        <v>46107</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4880,38 +4880,38 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="G111" t="n">
-        <v>50.45</v>
+        <v>188</v>
       </c>
       <c r="H111" t="n">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>-10110</v>
+        <v>-188267</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>46022</v>
+        <v>46108</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4920,24 +4920,24 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>198</v>
+        <v>1000</v>
       </c>
       <c r="G112" t="n">
-        <v>50.7</v>
+        <v>183</v>
       </c>
       <c r="H112" t="n">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>-10059</v>
+        <v>-183260</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46052</v>
+        <v>46108</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>195</v>
       </c>
       <c r="G113" t="n">
-        <v>51.3</v>
+        <v>51.45</v>
       </c>
       <c r="H113" t="n">
         <v>20</v>
@@ -4972,26 +4972,26 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>-10024</v>
+        <v>-10053</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46079</v>
+        <v>46108</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>186</v>
+        <v>48</v>
       </c>
       <c r="G114" t="n">
-        <v>53.85</v>
+        <v>104.65</v>
       </c>
       <c r="H114" t="n">
         <v>20</v>
@@ -5012,61 +5012,61 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>-10036</v>
+        <v>-5043</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>009816</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>5000</v>
+        <v>93</v>
       </c>
       <c r="G115" t="n">
-        <v>36.2</v>
+        <v>10.44</v>
       </c>
       <c r="H115" t="n">
-        <v>257</v>
+        <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>543</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>180200</v>
+        <v>-972</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>009816</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>主動統一台股增長</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5076,37 +5076,37 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>14000</v>
+        <v>48</v>
       </c>
       <c r="G116" t="n">
-        <v>10.8</v>
+        <v>20.37</v>
       </c>
       <c r="H116" t="n">
-        <v>215</v>
+        <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>150834</v>
+        <v>-979</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46106</v>
+        <v>46112</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>009816</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5116,37 +5116,37 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>62</v>
+        <v>2794</v>
       </c>
       <c r="G117" t="n">
-        <v>10.78</v>
+        <v>20.51</v>
       </c>
       <c r="H117" t="n">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>648</v>
+        <v>-57485</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>主動統一台股增長</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5160,33 +5160,33 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>7000</v>
+        <v>48</v>
       </c>
       <c r="G118" t="n">
-        <v>20.84</v>
+        <v>104.4</v>
       </c>
       <c r="H118" t="n">
-        <v>207</v>
+        <v>20</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>-146087</v>
+        <v>-5031</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>主動統一台股增長</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>283</v>
+        <v>250</v>
       </c>
       <c r="G119" t="n">
-        <v>20.83</v>
+        <v>20.04</v>
       </c>
       <c r="H119" t="n">
         <v>20</v>
@@ -5212,26 +5212,26 @@
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>-5915</v>
+        <v>-5030</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46107</v>
+        <v>46122</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5240,38 +5240,38 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1000</v>
+        <v>212</v>
       </c>
       <c r="G120" t="n">
-        <v>188</v>
+        <v>23.67</v>
       </c>
       <c r="H120" t="n">
-        <v>267</v>
+        <v>20</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>-188267</v>
+        <v>-5038</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46108</v>
+        <v>46122</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5280,38 +5280,38 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1000</v>
+        <v>45</v>
       </c>
       <c r="G121" t="n">
-        <v>183</v>
+        <v>111.2</v>
       </c>
       <c r="H121" t="n">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>-183260</v>
+        <v>-5024</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46108</v>
+        <v>46125</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5320,118 +5320,118 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>195</v>
+        <v>2000</v>
       </c>
       <c r="G122" t="n">
-        <v>51.45</v>
+        <v>51.4</v>
       </c>
       <c r="H122" t="n">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>-10053</v>
+        <v>-102946</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46108</v>
+        <v>46126</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>48</v>
+        <v>2000</v>
       </c>
       <c r="G123" t="n">
-        <v>104.65</v>
+        <v>224.5</v>
       </c>
       <c r="H123" t="n">
-        <v>20</v>
+        <v>639</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>1347</v>
       </c>
       <c r="J123" t="n">
-        <v>-5043</v>
+        <v>447014</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46114</v>
+        <v>46126</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="G124" t="n">
-        <v>20.04</v>
+        <v>54.2</v>
       </c>
       <c r="H124" t="n">
-        <v>20</v>
+        <v>154</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="J124" t="n">
-        <v>-5030</v>
+        <v>107921</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46114</v>
+        <v>46126</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5440,38 +5440,38 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="G125" t="n">
-        <v>104.4</v>
+        <v>103</v>
       </c>
       <c r="H125" t="n">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>-5031</v>
+        <v>-103146</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46122</v>
+        <v>46127</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5480,38 +5480,38 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>212</v>
+        <v>1000</v>
       </c>
       <c r="G126" t="n">
-        <v>23.67</v>
+        <v>238.5</v>
       </c>
       <c r="H126" t="n">
-        <v>20</v>
+        <v>339</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>-5038</v>
+        <v>-238839</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46122</v>
+        <v>46127</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5520,259 +5520,19 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>45</v>
+        <v>1000</v>
       </c>
       <c r="G127" t="n">
-        <v>111.2</v>
+        <v>236.5</v>
       </c>
       <c r="H127" t="n">
-        <v>20</v>
+        <v>337</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>-5024</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>009816</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>凱基台灣TOP50</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>定期定額</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>買</t>
-        </is>
-      </c>
-      <c r="F128" t="n">
-        <v>93</v>
-      </c>
-      <c r="G128" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="H128" t="n">
-        <v>1</v>
-      </c>
-      <c r="I128" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" t="n">
-        <v>-972</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>00981A</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>主動統一台股增長</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>定期定額</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>買</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
-        <v>48</v>
-      </c>
-      <c r="G129" t="n">
-        <v>20.37</v>
-      </c>
-      <c r="H129" t="n">
-        <v>1</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" t="n">
-        <v>-979</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
-        <v>46125</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>台塑</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>波段操作</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>買</t>
-        </is>
-      </c>
-      <c r="F130" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G130" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="H130" t="n">
-        <v>146</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" t="n">
-        <v>-102946</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
-        <v>46126</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>台塑</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>波段操作</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>賣</t>
-        </is>
-      </c>
-      <c r="F131" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G131" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="H131" t="n">
-        <v>154</v>
-      </c>
-      <c r="I131" t="n">
-        <v>325</v>
-      </c>
-      <c r="J131" t="n">
-        <v>107921</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
-        <v>46126</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>啟碁</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>波段操作</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>賣</t>
-        </is>
-      </c>
-      <c r="F132" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G132" t="n">
-        <v>224.5</v>
-      </c>
-      <c r="H132" t="n">
-        <v>639</v>
-      </c>
-      <c r="I132" t="n">
-        <v>1347</v>
-      </c>
-      <c r="J132" t="n">
-        <v>447014</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>46126</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>6206</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>飛捷</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>波段操作</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>買</t>
-        </is>
-      </c>
-      <c r="F133" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G133" t="n">
-        <v>103</v>
-      </c>
-      <c r="H133" t="n">
-        <v>146</v>
-      </c>
-      <c r="I133" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" t="n">
-        <v>-103146</v>
+        <v>-236837</v>
       </c>
     </row>
   </sheetData>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5535,6 +5535,86 @@
         <v>-236837</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G128" t="n">
+        <v>242</v>
+      </c>
+      <c r="H128" t="n">
+        <v>689</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1452</v>
+      </c>
+      <c r="J128" t="n">
+        <v>481859</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G129" t="n">
+        <v>218</v>
+      </c>
+      <c r="H129" t="n">
+        <v>310</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>-218310</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:J139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5615,6 +5615,406 @@
         <v>-218310</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G130" t="n">
+        <v>205</v>
+      </c>
+      <c r="H130" t="n">
+        <v>292</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-205292</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>00757</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>統一FANG+</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>43</v>
+      </c>
+      <c r="G131" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="H131" t="n">
+        <v>20</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>-5120</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>00631L</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>元大台灣50正2</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>179</v>
+      </c>
+      <c r="G132" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="H132" t="n">
+        <v>20</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>-5111</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>00713</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>元大台灣高息低波</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>爸爸合資</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>188</v>
+      </c>
+      <c r="G133" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="H133" t="n">
+        <v>20</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>-10022</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>譜瑞-KY</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>100</v>
+      </c>
+      <c r="G134" t="n">
+        <v>618</v>
+      </c>
+      <c r="H134" t="n">
+        <v>88</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>-61888</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>4956</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>光鋐</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G135" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="H135" t="n">
+        <v>136</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-96236</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>6206</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>飛捷</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G136" t="n">
+        <v>105</v>
+      </c>
+      <c r="H136" t="n">
+        <v>149</v>
+      </c>
+      <c r="I136" t="n">
+        <v>315</v>
+      </c>
+      <c r="J136" t="n">
+        <v>104536</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G137" t="n">
+        <v>211</v>
+      </c>
+      <c r="H137" t="n">
+        <v>602</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1266</v>
+      </c>
+      <c r="J137" t="n">
+        <v>420132</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>00631L</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>元大台灣50正2</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>獲利賣出</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>945</v>
+      </c>
+      <c r="G138" t="n">
+        <v>29.48</v>
+      </c>
+      <c r="H138" t="n">
+        <v>39</v>
+      </c>
+      <c r="I138" t="n">
+        <v>27</v>
+      </c>
+      <c r="J138" t="n">
+        <v>27793</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>主動統一台股增長</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G139" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="H139" t="n">
+        <v>39</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>-27819</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J139"/>
+  <dimension ref="A1:J154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6015,6 +6015,606 @@
         <v>-27819</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>4956</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>光鋐</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G140" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="H140" t="n">
+        <v>70</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>-49370</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G141" t="n">
+        <v>233.5</v>
+      </c>
+      <c r="H141" t="n">
+        <v>332</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>-233832</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>6282</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>康舒</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G142" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="H142" t="n">
+        <v>359</v>
+      </c>
+      <c r="I142" t="n">
+        <v>756</v>
+      </c>
+      <c r="J142" t="n">
+        <v>250885</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2495</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>普安</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G143" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="H143" t="n">
+        <v>364</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>-255964</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>009816</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>凱基台灣TOP50</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>74</v>
+      </c>
+      <c r="G144" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="H144" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>-976</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>主動統一台股增長</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>35</v>
+      </c>
+      <c r="G145" t="n">
+        <v>27.87</v>
+      </c>
+      <c r="H145" t="n">
+        <v>1</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>-976</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2495</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>普安</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G146" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="H146" t="n">
+        <v>290</v>
+      </c>
+      <c r="I146" t="n">
+        <v>611</v>
+      </c>
+      <c r="J146" t="n">
+        <v>202849</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2495</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>普安</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G147" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="H147" t="n">
+        <v>58</v>
+      </c>
+      <c r="I147" t="n">
+        <v>122</v>
+      </c>
+      <c r="J147" t="n">
+        <v>40720</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G148" t="n">
+        <v>256</v>
+      </c>
+      <c r="H148" t="n">
+        <v>364</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>-256364</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>譜瑞-KY</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>103</v>
+      </c>
+      <c r="G149" t="n">
+        <v>600</v>
+      </c>
+      <c r="H149" t="n">
+        <v>88</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>-61888</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>00631L</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>元大台灣50正2</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>154</v>
+      </c>
+      <c r="G150" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="H150" t="n">
+        <v>20</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>-5022</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>00757</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>統一FANG+</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>40</v>
+      </c>
+      <c r="G151" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="H151" t="n">
+        <v>20</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>-5008</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>4956</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>光鋐</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G152" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="H152" t="n">
+        <v>72</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>-51172</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>4956</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>光鋐</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G153" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="H153" t="n">
+        <v>605</v>
+      </c>
+      <c r="I153" t="n">
+        <v>1274</v>
+      </c>
+      <c r="J153" t="n">
+        <v>422921</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>6202</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>盛群</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G154" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="H154" t="n">
+        <v>426</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>-299426</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J154"/>
+  <dimension ref="A1:J155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6615,6 +6615,46 @@
         <v>-299426</v>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>6202</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>盛群</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G155" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="H155" t="n">
+        <v>389</v>
+      </c>
+      <c r="I155" t="n">
+        <v>820</v>
+      </c>
+      <c r="J155" t="n">
+        <v>272291</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J155"/>
+  <dimension ref="A1:J164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>00878</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>467</v>
+        <v>205</v>
       </c>
       <c r="G32" t="n">
-        <v>20.52</v>
+        <v>47.18</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
@@ -1732,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-9584</v>
+        <v>-9673</v>
       </c>
     </row>
     <row r="33">
@@ -1741,12 +1741,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00878</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>205</v>
+        <v>467</v>
       </c>
       <c r="G33" t="n">
-        <v>47.18</v>
+        <v>20.52</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-9673</v>
+        <v>-9584</v>
       </c>
     </row>
     <row r="34">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2920,38 +2920,38 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="G62" t="n">
-        <v>118.7</v>
+        <v>123</v>
       </c>
       <c r="H62" t="n">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>-5005</v>
+        <v>-123175</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45961</v>
+        <v>45953</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>197</v>
+        <v>42</v>
       </c>
       <c r="G63" t="n">
-        <v>51.35</v>
+        <v>118.7</v>
       </c>
       <c r="H63" t="n">
         <v>20</v>
@@ -2972,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>-10136</v>
+        <v>-5005</v>
       </c>
     </row>
     <row r="64">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>40</v>
+        <v>197</v>
       </c>
       <c r="G64" t="n">
-        <v>125.4</v>
+        <v>51.35</v>
       </c>
       <c r="H64" t="n">
         <v>20</v>
@@ -3012,12 +3012,12 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>-5036</v>
+        <v>-10136</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45968</v>
+        <v>45961</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G65" t="n">
-        <v>121.1</v>
+        <v>125.4</v>
       </c>
       <c r="H65" t="n">
         <v>20</v>
@@ -3052,26 +3052,26 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>-5106</v>
+        <v>-5036</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45968</v>
+        <v>45967</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3080,24 +3080,24 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>195</v>
+        <v>1000</v>
       </c>
       <c r="G66" t="n">
-        <v>51.3</v>
+        <v>116.5</v>
       </c>
       <c r="H66" t="n">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>-10024</v>
+        <v>-116666</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45975</v>
+        <v>45968</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>42</v>
       </c>
       <c r="G67" t="n">
-        <v>120.7</v>
+        <v>121.1</v>
       </c>
       <c r="H67" t="n">
         <v>20</v>
@@ -3132,26 +3132,26 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>-5089</v>
+        <v>-5106</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45982</v>
+        <v>45968</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>43</v>
+        <v>195</v>
       </c>
       <c r="G68" t="n">
-        <v>117.15</v>
+        <v>51.3</v>
       </c>
       <c r="H68" t="n">
         <v>20</v>
@@ -3172,12 +3172,12 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>-5057</v>
+        <v>-10024</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45989</v>
+        <v>45975</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G69" t="n">
-        <v>123.05</v>
+        <v>120.7</v>
       </c>
       <c r="H69" t="n">
         <v>20</v>
@@ -3212,26 +3212,26 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>-5065</v>
+        <v>-5089</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45989</v>
+        <v>45982</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>200</v>
+        <v>43</v>
       </c>
       <c r="G70" t="n">
-        <v>50.45</v>
+        <v>117.15</v>
       </c>
       <c r="H70" t="n">
         <v>20</v>
@@ -3252,26 +3252,26 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>-10110</v>
+        <v>-5057</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45996</v>
+        <v>45989</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>41</v>
+        <v>200</v>
       </c>
       <c r="G71" t="n">
-        <v>123.15</v>
+        <v>50.45</v>
       </c>
       <c r="H71" t="n">
         <v>20</v>
@@ -3292,12 +3292,12 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>-5069</v>
+        <v>-10110</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46003</v>
+        <v>45989</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>41</v>
       </c>
       <c r="G72" t="n">
-        <v>121.95</v>
+        <v>123.05</v>
       </c>
       <c r="H72" t="n">
         <v>20</v>
@@ -3332,12 +3332,12 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>-5020</v>
+        <v>-5065</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46013</v>
+        <v>45996</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G73" t="n">
-        <v>119.45</v>
+        <v>123.15</v>
       </c>
       <c r="H73" t="n">
         <v>20</v>
@@ -3372,12 +3372,12 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>-5037</v>
+        <v>-5069</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46017</v>
+        <v>46003</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G74" t="n">
-        <v>119.6</v>
+        <v>121.95</v>
       </c>
       <c r="H74" t="n">
         <v>20</v>
@@ -3412,26 +3412,26 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>-5043</v>
+        <v>-5020</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>198</v>
+        <v>42</v>
       </c>
       <c r="G75" t="n">
-        <v>50.7</v>
+        <v>119.45</v>
       </c>
       <c r="H75" t="n">
         <v>20</v>
@@ -3452,12 +3452,12 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>-10059</v>
+        <v>-5037</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46031</v>
+        <v>46017</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="G76" t="n">
-        <v>117.65</v>
+        <v>119.6</v>
       </c>
       <c r="H76" t="n">
         <v>20</v>
@@ -3492,26 +3492,26 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>-10020</v>
+        <v>-5043</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46035</v>
+        <v>46022</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3520,38 +3520,38 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2000</v>
+        <v>198</v>
       </c>
       <c r="G77" t="n">
-        <v>50.3</v>
+        <v>50.7</v>
       </c>
       <c r="H77" t="n">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>-100743</v>
+        <v>-10059</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46036</v>
+        <v>46031</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3560,24 +3560,24 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2000</v>
+        <v>85</v>
       </c>
       <c r="G78" t="n">
-        <v>54.4</v>
+        <v>117.65</v>
       </c>
       <c r="H78" t="n">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>-108955</v>
+        <v>-10020</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46038</v>
+        <v>46035</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3600,24 +3600,24 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G79" t="n">
-        <v>55</v>
+        <v>50.3</v>
       </c>
       <c r="H79" t="n">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>-55078</v>
+        <v>-100743</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46041</v>
+        <v>46036</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3640,24 +3640,24 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G80" t="n">
-        <v>58</v>
+        <v>54.4</v>
       </c>
       <c r="H80" t="n">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>-58082</v>
+        <v>-108955</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46045</v>
+        <v>46038</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3683,35 +3683,35 @@
         <v>1000</v>
       </c>
       <c r="G81" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H81" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>-58082</v>
+        <v>-55078</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46045</v>
+        <v>46041</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3720,24 +3720,24 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="G82" t="n">
-        <v>114.3</v>
+        <v>58</v>
       </c>
       <c r="H82" t="n">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>-5049</v>
+        <v>-58082</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46049</v>
+        <v>46045</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -3763,35 +3763,35 @@
         <v>1000</v>
       </c>
       <c r="G83" t="n">
-        <v>56.5</v>
+        <v>58</v>
       </c>
       <c r="H83" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>-56580</v>
+        <v>-58082</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46049</v>
+        <v>46045</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3800,24 +3800,24 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="G84" t="n">
-        <v>55</v>
+        <v>114.3</v>
       </c>
       <c r="H84" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>-55078</v>
+        <v>-5049</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46051</v>
+        <v>46049</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -3843,35 +3843,35 @@
         <v>1000</v>
       </c>
       <c r="G85" t="n">
-        <v>53.7</v>
+        <v>56.5</v>
       </c>
       <c r="H85" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>-53776</v>
+        <v>-56580</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46052</v>
+        <v>46049</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3880,24 +3880,24 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="G86" t="n">
-        <v>114.1</v>
+        <v>55</v>
       </c>
       <c r="H86" t="n">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>-5040</v>
+        <v>-55078</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -3923,16 +3923,16 @@
         <v>1000</v>
       </c>
       <c r="G87" t="n">
-        <v>50.1</v>
+        <v>53.7</v>
       </c>
       <c r="H87" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>-50171</v>
+        <v>-53776</v>
       </c>
     </row>
     <row r="88">
@@ -3977,7 +3977,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46055</v>
+        <v>46052</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -4003,35 +4003,35 @@
         <v>1000</v>
       </c>
       <c r="G89" t="n">
-        <v>48.3</v>
+        <v>50.1</v>
       </c>
       <c r="H89" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>-48368</v>
+        <v>-50171</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46062</v>
+        <v>46052</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4040,24 +4040,24 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="G90" t="n">
-        <v>48.15</v>
+        <v>114.1</v>
       </c>
       <c r="H90" t="n">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>-48218</v>
+        <v>-5040</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -4083,35 +4083,35 @@
         <v>1000</v>
       </c>
       <c r="G91" t="n">
-        <v>49</v>
+        <v>48.3</v>
       </c>
       <c r="H91" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>-49069</v>
+        <v>-48368</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4120,24 +4120,24 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="G92" t="n">
-        <v>110.35</v>
+        <v>48.15</v>
       </c>
       <c r="H92" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>-5096</v>
+        <v>-48218</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46076</v>
+        <v>46062</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -4163,35 +4163,35 @@
         <v>1000</v>
       </c>
       <c r="G93" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H93" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>-50071</v>
+        <v>-49069</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46079</v>
+        <v>46064</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>186</v>
+        <v>46</v>
       </c>
       <c r="G94" t="n">
-        <v>53.85</v>
+        <v>110.35</v>
       </c>
       <c r="H94" t="n">
         <v>20</v>
@@ -4212,26 +4212,26 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>-10036</v>
+        <v>-5096</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46079</v>
+        <v>46076</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4240,38 +4240,38 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>47</v>
+        <v>1000</v>
       </c>
       <c r="G95" t="n">
-        <v>106.9</v>
+        <v>50</v>
       </c>
       <c r="H95" t="n">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>-5044</v>
+        <v>-50071</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46087</v>
+        <v>46079</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="G96" t="n">
-        <v>112.45</v>
+        <v>53.85</v>
       </c>
       <c r="H96" t="n">
         <v>20</v>
@@ -4292,21 +4292,21 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>-5080</v>
+        <v>-10036</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46092</v>
+        <v>46079</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>009816</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="G97" t="n">
-        <v>10.96</v>
+        <v>106.9</v>
       </c>
       <c r="H97" t="n">
         <v>20</v>
@@ -4332,21 +4332,21 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>-700</v>
+        <v>-5044</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46092</v>
+        <v>46087</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>009816</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4360,33 +4360,33 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>14000</v>
+        <v>45</v>
       </c>
       <c r="G98" t="n">
-        <v>10.95</v>
+        <v>112.45</v>
       </c>
       <c r="H98" t="n">
-        <v>218</v>
+        <v>20</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>-153518</v>
+        <v>-5080</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46094</v>
+        <v>46092</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>009816</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4400,10 +4400,10 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="G99" t="n">
-        <v>111.7</v>
+        <v>10.96</v>
       </c>
       <c r="H99" t="n">
         <v>20</v>
@@ -4412,26 +4412,26 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>-5046</v>
+        <v>-700</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46099</v>
+        <v>46092</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>009816</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4440,38 +4440,38 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="G100" t="n">
-        <v>35.9</v>
+        <v>10.95</v>
       </c>
       <c r="H100" t="n">
-        <v>102</v>
+        <v>218</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>-71902</v>
+        <v>-153518</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46099</v>
+        <v>46094</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4480,33 +4480,33 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3000</v>
+        <v>45</v>
       </c>
       <c r="G101" t="n">
-        <v>35.95</v>
+        <v>111.7</v>
       </c>
       <c r="H101" t="n">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>-108003</v>
+        <v>-5046</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4523,30 +4523,30 @@
         <v>2000</v>
       </c>
       <c r="G102" t="n">
-        <v>33.55</v>
+        <v>35.9</v>
       </c>
       <c r="H102" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>-67195</v>
+        <v>-71902</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4560,19 +4560,19 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G103" t="n">
-        <v>33.3</v>
+        <v>35.95</v>
       </c>
       <c r="H103" t="n">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>-33347</v>
+        <v>-108003</v>
       </c>
     </row>
     <row r="104">
@@ -4603,7 +4603,7 @@
         <v>2000</v>
       </c>
       <c r="G104" t="n">
-        <v>33.5</v>
+        <v>33.55</v>
       </c>
       <c r="H104" t="n">
         <v>95</v>
@@ -4612,26 +4612,26 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>-67095</v>
+        <v>-67195</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4640,38 +4640,38 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="G105" t="n">
-        <v>109.45</v>
+        <v>33.3</v>
       </c>
       <c r="H105" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>-5055</v>
+        <v>-33347</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46106</v>
+        <v>46100</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>主動統一台股增長</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4680,33 +4680,33 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="G106" t="n">
-        <v>20.84</v>
+        <v>33.5</v>
       </c>
       <c r="H106" t="n">
-        <v>207</v>
+        <v>95</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>-146087</v>
+        <v>-67095</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46106</v>
+        <v>46101</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>009816</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4716,23 +4716,23 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>14000</v>
+        <v>46</v>
       </c>
       <c r="G107" t="n">
-        <v>10.8</v>
+        <v>109.45</v>
       </c>
       <c r="H107" t="n">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="I107" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>150834</v>
+        <v>-5055</v>
       </c>
     </row>
     <row r="108">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>009816</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>主動統一台股增長</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4756,14 +4756,14 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>283</v>
+        <v>62</v>
       </c>
       <c r="G108" t="n">
-        <v>20.83</v>
+        <v>10.78</v>
       </c>
       <c r="H108" t="n">
         <v>20</v>
@@ -4772,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>-5915</v>
+        <v>648</v>
       </c>
     </row>
     <row r="109">
@@ -4800,19 +4800,19 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>62</v>
+        <v>14000</v>
       </c>
       <c r="G109" t="n">
-        <v>10.78</v>
+        <v>10.8</v>
       </c>
       <c r="H109" t="n">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="J109" t="n">
-        <v>648</v>
+        <v>150834</v>
       </c>
     </row>
     <row r="110">
@@ -4821,57 +4821,57 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>主動統一台股增長</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="G110" t="n">
-        <v>36.2</v>
+        <v>20.84</v>
       </c>
       <c r="H110" t="n">
-        <v>257</v>
+        <v>207</v>
       </c>
       <c r="I110" t="n">
-        <v>543</v>
+        <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>180200</v>
+        <v>-146087</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>主動統一台股增長</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4880,33 +4880,33 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1000</v>
+        <v>283</v>
       </c>
       <c r="G111" t="n">
-        <v>188</v>
+        <v>20.83</v>
       </c>
       <c r="H111" t="n">
-        <v>267</v>
+        <v>20</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>-188267</v>
+        <v>-5915</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4916,42 +4916,42 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="G112" t="n">
-        <v>183</v>
+        <v>36.2</v>
       </c>
       <c r="H112" t="n">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>543</v>
       </c>
       <c r="J112" t="n">
-        <v>-183260</v>
+        <v>180200</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4960,19 +4960,19 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>195</v>
+        <v>1000</v>
       </c>
       <c r="G113" t="n">
-        <v>51.45</v>
+        <v>188</v>
       </c>
       <c r="H113" t="n">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>-10053</v>
+        <v>-188267</v>
       </c>
     </row>
     <row r="114">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>48</v>
+        <v>195</v>
       </c>
       <c r="G114" t="n">
-        <v>104.65</v>
+        <v>51.45</v>
       </c>
       <c r="H114" t="n">
         <v>20</v>
@@ -5012,21 +5012,21 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>-5043</v>
+        <v>-10053</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46111</v>
+        <v>46108</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>009816</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5040,38 +5040,38 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="G115" t="n">
-        <v>10.44</v>
+        <v>104.65</v>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>-972</v>
+        <v>-5043</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46111</v>
+        <v>46108</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>主動統一台股增長</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5080,33 +5080,33 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="G116" t="n">
-        <v>20.37</v>
+        <v>183</v>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>-979</v>
+        <v>-183260</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>009816</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5120,33 +5120,33 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>2794</v>
+        <v>93</v>
       </c>
       <c r="G117" t="n">
-        <v>20.51</v>
+        <v>10.44</v>
       </c>
       <c r="H117" t="n">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>-57485</v>
+        <v>-972</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46114</v>
+        <v>46111</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>主動統一台股增長</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5163,21 +5163,21 @@
         <v>48</v>
       </c>
       <c r="G118" t="n">
-        <v>104.4</v>
+        <v>20.37</v>
       </c>
       <c r="H118" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>-5031</v>
+        <v>-979</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46114</v>
+        <v>46112</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -5200,33 +5200,33 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>250</v>
+        <v>2794</v>
       </c>
       <c r="G119" t="n">
-        <v>20.04</v>
+        <v>20.51</v>
       </c>
       <c r="H119" t="n">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>-5030</v>
+        <v>-57485</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46122</v>
+        <v>46114</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>212</v>
+        <v>48</v>
       </c>
       <c r="G120" t="n">
-        <v>23.67</v>
+        <v>104.4</v>
       </c>
       <c r="H120" t="n">
         <v>20</v>
@@ -5252,21 +5252,21 @@
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>-5038</v>
+        <v>-5031</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46122</v>
+        <v>46114</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>45</v>
+        <v>250</v>
       </c>
       <c r="G121" t="n">
-        <v>111.2</v>
+        <v>20.04</v>
       </c>
       <c r="H121" t="n">
         <v>20</v>
@@ -5292,26 +5292,26 @@
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>-5024</v>
+        <v>-5030</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46125</v>
+        <v>46122</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5320,64 +5320,64 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>2000</v>
+        <v>45</v>
       </c>
       <c r="G122" t="n">
-        <v>51.4</v>
+        <v>111.2</v>
       </c>
       <c r="H122" t="n">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>-102946</v>
+        <v>-5024</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46126</v>
+        <v>46122</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>2000</v>
+        <v>212</v>
       </c>
       <c r="G123" t="n">
-        <v>224.5</v>
+        <v>23.67</v>
       </c>
       <c r="H123" t="n">
-        <v>639</v>
+        <v>20</v>
       </c>
       <c r="I123" t="n">
-        <v>1347</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>447014</v>
+        <v>-5038</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46126</v>
+        <v>46125</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -5396,23 +5396,23 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F124" t="n">
         <v>2000</v>
       </c>
       <c r="G124" t="n">
-        <v>54.2</v>
+        <v>51.4</v>
       </c>
       <c r="H124" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I124" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>107921</v>
+        <v>-102946</v>
       </c>
     </row>
     <row r="125">
@@ -5421,12 +5421,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5436,37 +5436,37 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G125" t="n">
-        <v>103</v>
+        <v>224.5</v>
       </c>
       <c r="H125" t="n">
-        <v>146</v>
+        <v>639</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>1347</v>
       </c>
       <c r="J125" t="n">
-        <v>-103146</v>
+        <v>447014</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5476,37 +5476,37 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G126" t="n">
-        <v>238.5</v>
+        <v>54.2</v>
       </c>
       <c r="H126" t="n">
-        <v>339</v>
+        <v>154</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="J126" t="n">
-        <v>-238839</v>
+        <v>107921</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5523,21 +5523,21 @@
         <v>1000</v>
       </c>
       <c r="G127" t="n">
-        <v>236.5</v>
+        <v>103</v>
       </c>
       <c r="H127" t="n">
-        <v>337</v>
+        <v>146</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>-236837</v>
+        <v>-103146</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46134</v>
+        <v>46127</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -5556,28 +5556,28 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G128" t="n">
-        <v>242</v>
+        <v>238.5</v>
       </c>
       <c r="H128" t="n">
-        <v>689</v>
+        <v>339</v>
       </c>
       <c r="I128" t="n">
-        <v>1452</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>481859</v>
+        <v>-238839</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46135</v>
+        <v>46127</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -5603,21 +5603,21 @@
         <v>1000</v>
       </c>
       <c r="G129" t="n">
-        <v>218</v>
+        <v>236.5</v>
       </c>
       <c r="H129" t="n">
-        <v>310</v>
+        <v>337</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>-218310</v>
+        <v>-236837</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46136</v>
+        <v>46134</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -5636,42 +5636,42 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G130" t="n">
-        <v>205</v>
+        <v>242</v>
       </c>
       <c r="H130" t="n">
-        <v>292</v>
+        <v>689</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>1452</v>
       </c>
       <c r="J130" t="n">
-        <v>-205292</v>
+        <v>481859</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5680,19 +5680,19 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>43</v>
+        <v>1000</v>
       </c>
       <c r="G131" t="n">
-        <v>118.6</v>
+        <v>218</v>
       </c>
       <c r="H131" t="n">
-        <v>20</v>
+        <v>310</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>-5120</v>
+        <v>-218310</v>
       </c>
     </row>
     <row r="132">
@@ -5701,17 +5701,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5720,19 +5720,19 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>179</v>
+        <v>1000</v>
       </c>
       <c r="G132" t="n">
-        <v>28.44</v>
+        <v>205</v>
       </c>
       <c r="H132" t="n">
-        <v>20</v>
+        <v>292</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>-5111</v>
+        <v>-205292</v>
       </c>
     </row>
     <row r="133">
@@ -5741,17 +5741,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5760,10 +5760,10 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="G133" t="n">
-        <v>53.2</v>
+        <v>118.6</v>
       </c>
       <c r="H133" t="n">
         <v>20</v>
@@ -5772,26 +5772,26 @@
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>-10022</v>
+        <v>-5120</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46139</v>
+        <v>46136</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5800,38 +5800,38 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="G134" t="n">
-        <v>618</v>
+        <v>28.44</v>
       </c>
       <c r="H134" t="n">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>-61888</v>
+        <v>-5111</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46140</v>
+        <v>46136</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5840,33 +5840,33 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>2000</v>
+        <v>188</v>
       </c>
       <c r="G135" t="n">
-        <v>48.05</v>
+        <v>53.2</v>
       </c>
       <c r="H135" t="n">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="I135" t="n">
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>-96236</v>
+        <v>-10022</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46140</v>
+        <v>46139</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5876,23 +5876,23 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="G136" t="n">
-        <v>105</v>
+        <v>618</v>
       </c>
       <c r="H136" t="n">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="I136" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>104536</v>
+        <v>-61888</v>
       </c>
     </row>
     <row r="137">
@@ -5901,38 +5901,38 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>主動統一台股增長</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>2000</v>
+        <v>35</v>
       </c>
       <c r="G137" t="n">
-        <v>211</v>
+        <v>27.87</v>
       </c>
       <c r="H137" t="n">
-        <v>602</v>
+        <v>1</v>
       </c>
       <c r="I137" t="n">
-        <v>1266</v>
+        <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>420132</v>
+        <v>-976</v>
       </c>
     </row>
     <row r="138">
@@ -5941,38 +5941,38 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>主動統一台股增長</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>獲利賣出</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>945</v>
+        <v>1000</v>
       </c>
       <c r="G138" t="n">
-        <v>29.48</v>
+        <v>27.78</v>
       </c>
       <c r="H138" t="n">
         <v>39</v>
       </c>
       <c r="I138" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>27793</v>
+        <v>-27819</v>
       </c>
     </row>
     <row r="139">
@@ -5981,57 +5981,57 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>主動統一台股增長</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>獲利賣出</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1000</v>
+        <v>945</v>
       </c>
       <c r="G139" t="n">
-        <v>27.78</v>
+        <v>29.48</v>
       </c>
       <c r="H139" t="n">
         <v>39</v>
       </c>
       <c r="I139" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J139" t="n">
-        <v>-27819</v>
+        <v>27793</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46146</v>
+        <v>46140</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>009816</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6040,33 +6040,33 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1000</v>
+        <v>74</v>
       </c>
       <c r="G140" t="n">
-        <v>49.3</v>
+        <v>13.17</v>
       </c>
       <c r="H140" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>-49370</v>
+        <v>-976</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46148</v>
+        <v>46140</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6080,33 +6080,33 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G141" t="n">
-        <v>233.5</v>
+        <v>48.05</v>
       </c>
       <c r="H141" t="n">
-        <v>332</v>
+        <v>136</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>-233832</v>
+        <v>-96236</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46148</v>
+        <v>46140</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6120,33 +6120,33 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="G142" t="n">
-        <v>50.4</v>
+        <v>211</v>
       </c>
       <c r="H142" t="n">
-        <v>359</v>
+        <v>602</v>
       </c>
       <c r="I142" t="n">
-        <v>756</v>
+        <v>1266</v>
       </c>
       <c r="J142" t="n">
-        <v>250885</v>
+        <v>420132</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46148</v>
+        <v>46140</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6156,42 +6156,42 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="G143" t="n">
-        <v>42.6</v>
+        <v>105</v>
       </c>
       <c r="H143" t="n">
-        <v>364</v>
+        <v>149</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="J143" t="n">
-        <v>-255964</v>
+        <v>104536</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>009816</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -6200,38 +6200,38 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>74</v>
+        <v>1000</v>
       </c>
       <c r="G144" t="n">
-        <v>13.17</v>
+        <v>49.3</v>
       </c>
       <c r="H144" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>-976</v>
+        <v>-49370</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>主動統一台股增長</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -6240,33 +6240,33 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>35</v>
+        <v>1000</v>
       </c>
       <c r="G145" t="n">
-        <v>27.87</v>
+        <v>233.5</v>
       </c>
       <c r="H145" t="n">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="I145" t="n">
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>-976</v>
+        <v>-233832</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6283,21 +6283,21 @@
         <v>5000</v>
       </c>
       <c r="G146" t="n">
-        <v>40.75</v>
+        <v>50.4</v>
       </c>
       <c r="H146" t="n">
-        <v>290</v>
+        <v>359</v>
       </c>
       <c r="I146" t="n">
-        <v>611</v>
+        <v>756</v>
       </c>
       <c r="J146" t="n">
-        <v>202849</v>
+        <v>250885</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -6316,23 +6316,23 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="G147" t="n">
-        <v>40.9</v>
+        <v>42.6</v>
       </c>
       <c r="H147" t="n">
-        <v>58</v>
+        <v>364</v>
       </c>
       <c r="I147" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>40720</v>
+        <v>-255964</v>
       </c>
     </row>
     <row r="148">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6356,23 +6356,23 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="G148" t="n">
-        <v>256</v>
+        <v>40.75</v>
       </c>
       <c r="H148" t="n">
-        <v>364</v>
+        <v>290</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>611</v>
       </c>
       <c r="J148" t="n">
-        <v>-256364</v>
+        <v>202849</v>
       </c>
     </row>
     <row r="149">
@@ -6417,61 +6417,61 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>154</v>
+        <v>1000</v>
       </c>
       <c r="G150" t="n">
-        <v>32.48</v>
+        <v>40.9</v>
       </c>
       <c r="H150" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="J150" t="n">
-        <v>-5022</v>
+        <v>40720</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6480,19 +6480,19 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="G151" t="n">
-        <v>124.7</v>
+        <v>256</v>
       </c>
       <c r="H151" t="n">
-        <v>20</v>
+        <v>364</v>
       </c>
       <c r="I151" t="n">
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>-5008</v>
+        <v>-256364</v>
       </c>
     </row>
     <row r="152">
@@ -6501,17 +6501,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -6520,24 +6520,24 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1000</v>
+        <v>154</v>
       </c>
       <c r="G152" t="n">
-        <v>51.1</v>
+        <v>32.48</v>
       </c>
       <c r="H152" t="n">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>-51172</v>
+        <v>-5022</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -6556,42 +6556,42 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="G153" t="n">
-        <v>47.2</v>
+        <v>51.1</v>
       </c>
       <c r="H153" t="n">
-        <v>605</v>
+        <v>72</v>
       </c>
       <c r="I153" t="n">
-        <v>1274</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>422921</v>
+        <v>-51172</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -6600,59 +6600,419 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>5000</v>
+        <v>40</v>
       </c>
       <c r="G154" t="n">
-        <v>59.8</v>
+        <v>124.7</v>
       </c>
       <c r="H154" t="n">
-        <v>426</v>
+        <v>20</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>-299426</v>
+        <v>-5008</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>4956</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>光鋐</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G155" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="H155" t="n">
+        <v>605</v>
+      </c>
+      <c r="I155" t="n">
+        <v>1274</v>
+      </c>
+      <c r="J155" t="n">
+        <v>422921</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>6202</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>盛群</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G156" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="H156" t="n">
+        <v>426</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>-299426</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
         <v>46155</v>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>6202</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>盛群</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="D157" t="inlineStr">
         <is>
           <t>波段操作</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="E157" t="inlineStr">
         <is>
           <t>賣</t>
         </is>
       </c>
-      <c r="F155" t="n">
+      <c r="F157" t="n">
         <v>5000</v>
       </c>
-      <c r="G155" t="n">
+      <c r="G157" t="n">
         <v>54.7</v>
       </c>
-      <c r="H155" t="n">
+      <c r="H157" t="n">
         <v>389</v>
       </c>
-      <c r="I155" t="n">
+      <c r="I157" t="n">
         <v>820</v>
       </c>
-      <c r="J155" t="n">
+      <c r="J157" t="n">
         <v>272291</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>00631L</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>元大台灣50正2</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>159</v>
+      </c>
+      <c r="G158" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="H158" t="n">
+        <v>20</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>-5028</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>00757</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>統一FANG+</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>39</v>
+      </c>
+      <c r="G159" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="H159" t="n">
+        <v>7</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>-5050</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G160" t="n">
+        <v>106</v>
+      </c>
+      <c r="H160" t="n">
+        <v>151</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>-106151</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G161" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="H161" t="n">
+        <v>148</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>-104648</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G162" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="H162" t="n">
+        <v>144</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>-101644</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G163" t="n">
+        <v>109</v>
+      </c>
+      <c r="H163" t="n">
+        <v>310</v>
+      </c>
+      <c r="I163" t="n">
+        <v>654</v>
+      </c>
+      <c r="J163" t="n">
+        <v>217036</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G164" t="n">
+        <v>163</v>
+      </c>
+      <c r="H164" t="n">
+        <v>696</v>
+      </c>
+      <c r="I164" t="n">
+        <v>1467</v>
+      </c>
+      <c r="J164" t="n">
+        <v>486837</v>
       </c>
     </row>
   </sheetData>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J164"/>
+  <dimension ref="A1:J165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7015,6 +7015,46 @@
         <v>486837</v>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>群創</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G165" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="H165" t="n">
+        <v>275</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>-193775</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交易記錄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="交易記錄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J165"/>
+  <dimension ref="A1:J166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7055,6 +7055,46 @@
         <v>-193775</v>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>群創</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G166" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="H166" t="n">
+        <v>268</v>
+      </c>
+      <c r="I166" t="n">
+        <v>565</v>
+      </c>
+      <c r="J166" t="n">
+        <v>187667</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="交易記錄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交易記錄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J166"/>
+  <dimension ref="A1:J167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7095,6 +7095,46 @@
         <v>187667</v>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>譜瑞-KY</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>77</v>
+      </c>
+      <c r="G167" t="n">
+        <v>800</v>
+      </c>
+      <c r="H167" t="n">
+        <v>87</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>-61687</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J167"/>
+  <dimension ref="A1:J169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7135,6 +7135,86 @@
         <v>-61687</v>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>00631L</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>元大台灣50正2</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>155</v>
+      </c>
+      <c r="G168" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="H168" t="n">
+        <v>20</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>-5039</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>00757</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>統一FANG+</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>39</v>
+      </c>
+      <c r="G169" t="n">
+        <v>128.65</v>
+      </c>
+      <c r="H169" t="n">
+        <v>7</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>-5024</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J169"/>
+  <dimension ref="A1:J172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7215,6 +7215,126 @@
         <v>-5024</v>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>00631L</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>元大台灣50正2</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>136</v>
+      </c>
+      <c r="G170" t="n">
+        <v>36.85</v>
+      </c>
+      <c r="H170" t="n">
+        <v>20</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>-5032</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>00713</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>元大台灣高息低波</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>爸爸合資</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>177</v>
+      </c>
+      <c r="G171" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="H171" t="n">
+        <v>20</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>-10029</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>00757</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>統一FANG+</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>38</v>
+      </c>
+      <c r="G172" t="n">
+        <v>133.45</v>
+      </c>
+      <c r="H172" t="n">
+        <v>7</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>-5078</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J172"/>
+  <dimension ref="A1:J174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7335,6 +7335,86 @@
         <v>-5078</v>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>009816</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>凱基台灣TOP50</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>64</v>
+      </c>
+      <c r="G173" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="H173" t="n">
+        <v>1</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>-978</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>主動統一台股增長</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>30</v>
+      </c>
+      <c r="G174" t="n">
+        <v>32.14</v>
+      </c>
+      <c r="H174" t="n">
+        <v>1</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>-965</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交易記錄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="交易記錄" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J174"/>
+  <dimension ref="A1:J177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00878</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>200</v>
+        <v>475</v>
       </c>
       <c r="G34" t="n">
-        <v>48.4</v>
+        <v>20.29</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -1812,7 +1812,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-9681</v>
+        <v>-9639</v>
       </c>
     </row>
     <row r="35">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>00878</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>475</v>
+        <v>200</v>
       </c>
       <c r="G35" t="n">
-        <v>20.29</v>
+        <v>48.4</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
@@ -1852,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-9639</v>
+        <v>-9681</v>
       </c>
     </row>
     <row r="36">
@@ -3177,21 +3177,21 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45975</v>
+        <v>45971</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3200,38 +3200,38 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="G69" t="n">
-        <v>120.7</v>
+        <v>106</v>
       </c>
       <c r="H69" t="n">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>-5089</v>
+        <v>-106151</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45982</v>
+        <v>45973</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3240,38 +3240,38 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>43</v>
+        <v>1000</v>
       </c>
       <c r="G70" t="n">
-        <v>117.15</v>
+        <v>104.5</v>
       </c>
       <c r="H70" t="n">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>-5057</v>
+        <v>-104648</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45989</v>
+        <v>45975</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>200</v>
+        <v>42</v>
       </c>
       <c r="G71" t="n">
-        <v>50.45</v>
+        <v>120.7</v>
       </c>
       <c r="H71" t="n">
         <v>20</v>
@@ -3292,26 +3292,26 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>-10110</v>
+        <v>-5089</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45989</v>
+        <v>45975</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3320,24 +3320,24 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>41</v>
+        <v>1000</v>
       </c>
       <c r="G72" t="n">
-        <v>123.05</v>
+        <v>101.5</v>
       </c>
       <c r="H72" t="n">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>-5065</v>
+        <v>-101644</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45996</v>
+        <v>45982</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G73" t="n">
-        <v>123.15</v>
+        <v>117.15</v>
       </c>
       <c r="H73" t="n">
         <v>20</v>
@@ -3372,12 +3372,12 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>-5069</v>
+        <v>-5057</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46003</v>
+        <v>45989</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>41</v>
       </c>
       <c r="G74" t="n">
-        <v>121.95</v>
+        <v>123.05</v>
       </c>
       <c r="H74" t="n">
         <v>20</v>
@@ -3412,26 +3412,26 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>-5020</v>
+        <v>-5065</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46013</v>
+        <v>45989</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="G75" t="n">
-        <v>119.45</v>
+        <v>50.45</v>
       </c>
       <c r="H75" t="n">
         <v>20</v>
@@ -3452,12 +3452,12 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>-5037</v>
+        <v>-10110</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46017</v>
+        <v>45996</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G76" t="n">
-        <v>119.6</v>
+        <v>123.15</v>
       </c>
       <c r="H76" t="n">
         <v>20</v>
@@ -3492,26 +3492,26 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>-5043</v>
+        <v>-5069</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46022</v>
+        <v>46003</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>198</v>
+        <v>41</v>
       </c>
       <c r="G77" t="n">
-        <v>50.7</v>
+        <v>121.95</v>
       </c>
       <c r="H77" t="n">
         <v>20</v>
@@ -3532,12 +3532,12 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>-10059</v>
+        <v>-5020</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46031</v>
+        <v>46013</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="G78" t="n">
-        <v>117.65</v>
+        <v>119.45</v>
       </c>
       <c r="H78" t="n">
         <v>20</v>
@@ -3572,26 +3572,26 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>-10020</v>
+        <v>-5037</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46035</v>
+        <v>46017</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3600,38 +3600,38 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2000</v>
+        <v>42</v>
       </c>
       <c r="G79" t="n">
-        <v>50.3</v>
+        <v>119.6</v>
       </c>
       <c r="H79" t="n">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>-100743</v>
+        <v>-5043</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46036</v>
+        <v>46022</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3640,38 +3640,38 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2000</v>
+        <v>198</v>
       </c>
       <c r="G80" t="n">
-        <v>54.4</v>
+        <v>50.7</v>
       </c>
       <c r="H80" t="n">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>-108955</v>
+        <v>-10059</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3680,24 +3680,24 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="G81" t="n">
-        <v>55</v>
+        <v>117.65</v>
       </c>
       <c r="H81" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>-55078</v>
+        <v>-10020</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46041</v>
+        <v>46035</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3720,24 +3720,24 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G82" t="n">
-        <v>58</v>
+        <v>50.3</v>
       </c>
       <c r="H82" t="n">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>-58082</v>
+        <v>-100743</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -3760,64 +3760,64 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G83" t="n">
-        <v>58</v>
+        <v>54.4</v>
       </c>
       <c r="H83" t="n">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>-58082</v>
+        <v>-108955</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46045</v>
+        <v>46038</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>44</v>
+        <v>2000</v>
       </c>
       <c r="G84" t="n">
-        <v>114.3</v>
+        <v>109</v>
       </c>
       <c r="H84" t="n">
-        <v>20</v>
+        <v>310</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>654</v>
       </c>
       <c r="J84" t="n">
-        <v>-5049</v>
+        <v>217036</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46049</v>
+        <v>46038</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -3843,21 +3843,21 @@
         <v>1000</v>
       </c>
       <c r="G85" t="n">
-        <v>56.5</v>
+        <v>55</v>
       </c>
       <c r="H85" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>-56580</v>
+        <v>-55078</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46049</v>
+        <v>46041</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -3883,35 +3883,35 @@
         <v>1000</v>
       </c>
       <c r="G86" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H86" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>-55078</v>
+        <v>-58082</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46051</v>
+        <v>46045</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3920,38 +3920,38 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="G87" t="n">
-        <v>53.7</v>
+        <v>114.3</v>
       </c>
       <c r="H87" t="n">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>-53776</v>
+        <v>-5049</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3960,24 +3960,24 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>195</v>
+        <v>1000</v>
       </c>
       <c r="G88" t="n">
-        <v>51.3</v>
+        <v>58</v>
       </c>
       <c r="H88" t="n">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>-10024</v>
+        <v>-58082</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46052</v>
+        <v>46049</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -4003,35 +4003,35 @@
         <v>1000</v>
       </c>
       <c r="G89" t="n">
-        <v>50.1</v>
+        <v>56.5</v>
       </c>
       <c r="H89" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>-50171</v>
+        <v>-56580</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46052</v>
+        <v>46049</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4040,24 +4040,24 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="G90" t="n">
-        <v>114.1</v>
+        <v>55</v>
       </c>
       <c r="H90" t="n">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>-5040</v>
+        <v>-55078</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46055</v>
+        <v>46051</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -4083,21 +4083,21 @@
         <v>1000</v>
       </c>
       <c r="G91" t="n">
-        <v>48.3</v>
+        <v>53.7</v>
       </c>
       <c r="H91" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>-48368</v>
+        <v>-53776</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46062</v>
+        <v>46052</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -4123,35 +4123,35 @@
         <v>1000</v>
       </c>
       <c r="G92" t="n">
-        <v>48.15</v>
+        <v>50.1</v>
       </c>
       <c r="H92" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>-48218</v>
+        <v>-50171</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46062</v>
+        <v>46052</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4160,38 +4160,38 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="G93" t="n">
-        <v>49</v>
+        <v>114.1</v>
       </c>
       <c r="H93" t="n">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>-49069</v>
+        <v>-5040</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46064</v>
+        <v>46052</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>46</v>
+        <v>195</v>
       </c>
       <c r="G94" t="n">
-        <v>110.35</v>
+        <v>51.3</v>
       </c>
       <c r="H94" t="n">
         <v>20</v>
@@ -4212,12 +4212,12 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>-5096</v>
+        <v>-10024</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46076</v>
+        <v>46055</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -4243,35 +4243,35 @@
         <v>1000</v>
       </c>
       <c r="G95" t="n">
-        <v>50</v>
+        <v>48.3</v>
       </c>
       <c r="H95" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>-50071</v>
+        <v>-48368</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46079</v>
+        <v>46062</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4280,38 +4280,38 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>186</v>
+        <v>1000</v>
       </c>
       <c r="G96" t="n">
-        <v>53.85</v>
+        <v>48.15</v>
       </c>
       <c r="H96" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>-10036</v>
+        <v>-48218</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46079</v>
+        <v>46062</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4320,24 +4320,24 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>47</v>
+        <v>1000</v>
       </c>
       <c r="G97" t="n">
-        <v>106.9</v>
+        <v>49</v>
       </c>
       <c r="H97" t="n">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>-5044</v>
+        <v>-49069</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46087</v>
+        <v>46064</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G98" t="n">
-        <v>112.45</v>
+        <v>110.35</v>
       </c>
       <c r="H98" t="n">
         <v>20</v>
@@ -4372,26 +4372,26 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>-5080</v>
+        <v>-5096</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46092</v>
+        <v>46076</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>009816</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4400,38 +4400,38 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>62</v>
+        <v>1000</v>
       </c>
       <c r="G99" t="n">
-        <v>10.96</v>
+        <v>50</v>
       </c>
       <c r="H99" t="n">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>-700</v>
+        <v>-50071</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46092</v>
+        <v>46079</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>009816</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4440,24 +4440,24 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>14000</v>
+        <v>186</v>
       </c>
       <c r="G100" t="n">
-        <v>10.95</v>
+        <v>53.85</v>
       </c>
       <c r="H100" t="n">
-        <v>218</v>
+        <v>20</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>-153518</v>
+        <v>-10036</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46094</v>
+        <v>46079</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G101" t="n">
-        <v>111.7</v>
+        <v>106.9</v>
       </c>
       <c r="H101" t="n">
         <v>20</v>
@@ -4492,21 +4492,21 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>-5046</v>
+        <v>-5044</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46099</v>
+        <v>46085</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4516,42 +4516,42 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G102" t="n">
-        <v>35.9</v>
+        <v>163</v>
       </c>
       <c r="H102" t="n">
-        <v>102</v>
+        <v>696</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>1467</v>
       </c>
       <c r="J102" t="n">
-        <v>-71902</v>
+        <v>486837</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46099</v>
+        <v>46087</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4560,38 +4560,38 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3000</v>
+        <v>45</v>
       </c>
       <c r="G103" t="n">
-        <v>35.95</v>
+        <v>112.45</v>
       </c>
       <c r="H103" t="n">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>-108003</v>
+        <v>-5080</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>46100</v>
+        <v>46092</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>009816</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4600,38 +4600,38 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="G104" t="n">
-        <v>33.55</v>
+        <v>10.95</v>
       </c>
       <c r="H104" t="n">
-        <v>95</v>
+        <v>218</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>-67195</v>
+        <v>-153518</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46100</v>
+        <v>46092</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>009816</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4640,38 +4640,38 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1000</v>
+        <v>62</v>
       </c>
       <c r="G105" t="n">
-        <v>33.3</v>
+        <v>10.96</v>
       </c>
       <c r="H105" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>-33347</v>
+        <v>-700</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46100</v>
+        <v>46094</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4680,38 +4680,38 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2000</v>
+        <v>45</v>
       </c>
       <c r="G106" t="n">
-        <v>33.5</v>
+        <v>111.7</v>
       </c>
       <c r="H106" t="n">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>-67095</v>
+        <v>-5046</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46101</v>
+        <v>46099</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4720,118 +4720,118 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>46</v>
+        <v>2000</v>
       </c>
       <c r="G107" t="n">
-        <v>109.45</v>
+        <v>35.9</v>
       </c>
       <c r="H107" t="n">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>-5055</v>
+        <v>-71902</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>46106</v>
+        <v>46099</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>009816</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>62</v>
+        <v>3000</v>
       </c>
       <c r="G108" t="n">
-        <v>10.78</v>
+        <v>35.95</v>
       </c>
       <c r="H108" t="n">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>648</v>
+        <v>-108003</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>46106</v>
+        <v>46100</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>009816</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>14000</v>
+        <v>2000</v>
       </c>
       <c r="G109" t="n">
-        <v>10.8</v>
+        <v>33.55</v>
       </c>
       <c r="H109" t="n">
-        <v>215</v>
+        <v>95</v>
       </c>
       <c r="I109" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>150834</v>
+        <v>-67195</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>46106</v>
+        <v>46100</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>主動統一台股增長</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4840,38 +4840,38 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="G110" t="n">
-        <v>20.84</v>
+        <v>33.3</v>
       </c>
       <c r="H110" t="n">
-        <v>207</v>
+        <v>47</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>-146087</v>
+        <v>-33347</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>46106</v>
+        <v>46100</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>主動統一台股增長</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4880,118 +4880,118 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>283</v>
+        <v>2000</v>
       </c>
       <c r="G111" t="n">
-        <v>20.83</v>
+        <v>33.5</v>
       </c>
       <c r="H111" t="n">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>-5915</v>
+        <v>-67095</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>46106</v>
+        <v>46101</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>5000</v>
+        <v>46</v>
       </c>
       <c r="G112" t="n">
-        <v>36.2</v>
+        <v>109.45</v>
       </c>
       <c r="H112" t="n">
-        <v>257</v>
+        <v>20</v>
       </c>
       <c r="I112" t="n">
-        <v>543</v>
+        <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>180200</v>
+        <v>-5055</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>009816</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1000</v>
+        <v>14000</v>
       </c>
       <c r="G113" t="n">
-        <v>188</v>
+        <v>10.8</v>
       </c>
       <c r="H113" t="n">
-        <v>267</v>
+        <v>215</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="J113" t="n">
-        <v>-188267</v>
+        <v>150834</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>主動統一台股增長</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5000,33 +5000,33 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>195</v>
+        <v>7000</v>
       </c>
       <c r="G114" t="n">
-        <v>51.45</v>
+        <v>20.84</v>
       </c>
       <c r="H114" t="n">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>-10053</v>
+        <v>-146087</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>主動統一台股增長</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>48</v>
+        <v>283</v>
       </c>
       <c r="G115" t="n">
-        <v>104.65</v>
+        <v>20.83</v>
       </c>
       <c r="H115" t="n">
         <v>20</v>
@@ -5052,21 +5052,21 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>-5043</v>
+        <v>-5915</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5076,28 +5076,28 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="G116" t="n">
-        <v>183</v>
+        <v>36.2</v>
       </c>
       <c r="H116" t="n">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>543</v>
       </c>
       <c r="J116" t="n">
-        <v>-183260</v>
+        <v>180200</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46111</v>
+        <v>46106</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -5116,42 +5116,42 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="G117" t="n">
-        <v>10.44</v>
+        <v>10.78</v>
       </c>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>-972</v>
+        <v>648</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46111</v>
+        <v>46107</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>主動統一台股增長</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5160,38 +5160,38 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="G118" t="n">
-        <v>20.37</v>
+        <v>188</v>
       </c>
       <c r="H118" t="n">
-        <v>1</v>
+        <v>267</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>-979</v>
+        <v>-188267</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46112</v>
+        <v>46108</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5200,24 +5200,24 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>2794</v>
+        <v>195</v>
       </c>
       <c r="G119" t="n">
-        <v>20.51</v>
+        <v>51.45</v>
       </c>
       <c r="H119" t="n">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>-57485</v>
+        <v>-10053</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46114</v>
+        <v>46108</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>48</v>
       </c>
       <c r="G120" t="n">
-        <v>104.4</v>
+        <v>104.65</v>
       </c>
       <c r="H120" t="n">
         <v>20</v>
@@ -5252,26 +5252,26 @@
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>-5031</v>
+        <v>-5043</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46114</v>
+        <v>46108</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5280,33 +5280,33 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="G121" t="n">
-        <v>20.04</v>
+        <v>183</v>
       </c>
       <c r="H121" t="n">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>-5030</v>
+        <v>-183260</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46122</v>
+        <v>46111</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>009816</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5320,33 +5320,33 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="G122" t="n">
-        <v>111.2</v>
+        <v>10.44</v>
       </c>
       <c r="H122" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>-5024</v>
+        <v>-972</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46122</v>
+        <v>46111</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>主動統一台股增長</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5360,38 +5360,38 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>212</v>
+        <v>48</v>
       </c>
       <c r="G123" t="n">
-        <v>23.67</v>
+        <v>20.37</v>
       </c>
       <c r="H123" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>-5038</v>
+        <v>-979</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46125</v>
+        <v>46112</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5400,118 +5400,118 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>2000</v>
+        <v>2794</v>
       </c>
       <c r="G124" t="n">
-        <v>51.4</v>
+        <v>20.51</v>
       </c>
       <c r="H124" t="n">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>-102946</v>
+        <v>-57485</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46126</v>
+        <v>46114</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>2000</v>
+        <v>48</v>
       </c>
       <c r="G125" t="n">
-        <v>224.5</v>
+        <v>104.4</v>
       </c>
       <c r="H125" t="n">
-        <v>639</v>
+        <v>20</v>
       </c>
       <c r="I125" t="n">
-        <v>1347</v>
+        <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>447014</v>
+        <v>-5031</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46126</v>
+        <v>46114</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>2000</v>
+        <v>250</v>
       </c>
       <c r="G126" t="n">
-        <v>54.2</v>
+        <v>20.04</v>
       </c>
       <c r="H126" t="n">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="I126" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>107921</v>
+        <v>-5030</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46126</v>
+        <v>46122</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5520,38 +5520,38 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1000</v>
+        <v>212</v>
       </c>
       <c r="G127" t="n">
-        <v>103</v>
+        <v>23.67</v>
       </c>
       <c r="H127" t="n">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>-103146</v>
+        <v>-5038</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46127</v>
+        <v>46122</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5560,33 +5560,33 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1000</v>
+        <v>45</v>
       </c>
       <c r="G128" t="n">
-        <v>238.5</v>
+        <v>111.2</v>
       </c>
       <c r="H128" t="n">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>-238839</v>
+        <v>-5024</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46127</v>
+        <v>46125</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5600,33 +5600,33 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G129" t="n">
-        <v>236.5</v>
+        <v>51.4</v>
       </c>
       <c r="H129" t="n">
-        <v>337</v>
+        <v>146</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>-236837</v>
+        <v>-102946</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46134</v>
+        <v>46126</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5643,30 +5643,30 @@
         <v>2000</v>
       </c>
       <c r="G130" t="n">
-        <v>242</v>
+        <v>54.2</v>
       </c>
       <c r="H130" t="n">
-        <v>689</v>
+        <v>154</v>
       </c>
       <c r="I130" t="n">
-        <v>1452</v>
+        <v>325</v>
       </c>
       <c r="J130" t="n">
-        <v>481859</v>
+        <v>107921</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46135</v>
+        <v>46126</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -5683,21 +5683,21 @@
         <v>1000</v>
       </c>
       <c r="G131" t="n">
-        <v>218</v>
+        <v>103</v>
       </c>
       <c r="H131" t="n">
-        <v>310</v>
+        <v>146</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>-218310</v>
+        <v>-103146</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46136</v>
+        <v>46126</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -5716,42 +5716,42 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G132" t="n">
-        <v>205</v>
+        <v>224.5</v>
       </c>
       <c r="H132" t="n">
-        <v>292</v>
+        <v>639</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>1347</v>
       </c>
       <c r="J132" t="n">
-        <v>-205292</v>
+        <v>447014</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46136</v>
+        <v>46127</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5760,38 +5760,38 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>43</v>
+        <v>1000</v>
       </c>
       <c r="G133" t="n">
-        <v>118.6</v>
+        <v>236.5</v>
       </c>
       <c r="H133" t="n">
-        <v>20</v>
+        <v>337</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>-5120</v>
+        <v>-236837</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46136</v>
+        <v>46127</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5800,73 +5800,73 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>179</v>
+        <v>1000</v>
       </c>
       <c r="G134" t="n">
-        <v>28.44</v>
+        <v>238.5</v>
       </c>
       <c r="H134" t="n">
-        <v>20</v>
+        <v>339</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>-5111</v>
+        <v>-238839</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46136</v>
+        <v>46134</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>188</v>
+        <v>2000</v>
       </c>
       <c r="G135" t="n">
-        <v>53.2</v>
+        <v>242</v>
       </c>
       <c r="H135" t="n">
-        <v>20</v>
+        <v>689</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>1452</v>
       </c>
       <c r="J135" t="n">
-        <v>-10022</v>
+        <v>481859</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46139</v>
+        <v>46135</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5880,38 +5880,38 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G136" t="n">
-        <v>618</v>
+        <v>218</v>
       </c>
       <c r="H136" t="n">
-        <v>88</v>
+        <v>310</v>
       </c>
       <c r="I136" t="n">
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>-61888</v>
+        <v>-218310</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46140</v>
+        <v>46136</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>主動統一台股增長</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5920,33 +5920,33 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>35</v>
+        <v>188</v>
       </c>
       <c r="G137" t="n">
-        <v>27.87</v>
+        <v>53.2</v>
       </c>
       <c r="H137" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>-976</v>
+        <v>-10022</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46140</v>
+        <v>46136</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>主動統一台股增長</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -5960,78 +5960,78 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1000</v>
+        <v>179</v>
       </c>
       <c r="G138" t="n">
-        <v>27.78</v>
+        <v>28.44</v>
       </c>
       <c r="H138" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="I138" t="n">
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>-27819</v>
+        <v>-5111</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46140</v>
+        <v>46136</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>獲利賣出</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>945</v>
+        <v>43</v>
       </c>
       <c r="G139" t="n">
-        <v>29.48</v>
+        <v>118.6</v>
       </c>
       <c r="H139" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="I139" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>27793</v>
+        <v>-5120</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46140</v>
+        <v>46136</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>009816</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6040,33 +6040,33 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>74</v>
+        <v>1000</v>
       </c>
       <c r="G140" t="n">
-        <v>13.17</v>
+        <v>205</v>
       </c>
       <c r="H140" t="n">
-        <v>1</v>
+        <v>292</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>-976</v>
+        <v>-205292</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46140</v>
+        <v>46139</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6080,19 +6080,19 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="G141" t="n">
-        <v>48.05</v>
+        <v>618</v>
       </c>
       <c r="H141" t="n">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>-96236</v>
+        <v>-61888</v>
       </c>
     </row>
     <row r="142">
@@ -6101,38 +6101,38 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>主動統一台股增長</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>2000</v>
+        <v>35</v>
       </c>
       <c r="G142" t="n">
-        <v>211</v>
+        <v>27.87</v>
       </c>
       <c r="H142" t="n">
-        <v>602</v>
+        <v>1</v>
       </c>
       <c r="I142" t="n">
-        <v>1266</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>420132</v>
+        <v>-976</v>
       </c>
     </row>
     <row r="143">
@@ -6141,83 +6141,83 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>主動統一台股增長</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F143" t="n">
         <v>1000</v>
       </c>
       <c r="G143" t="n">
-        <v>105</v>
+        <v>27.78</v>
       </c>
       <c r="H143" t="n">
-        <v>149</v>
+        <v>39</v>
       </c>
       <c r="I143" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>104536</v>
+        <v>-27819</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46146</v>
+        <v>46140</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>獲利賣出</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1000</v>
+        <v>945</v>
       </c>
       <c r="G144" t="n">
-        <v>49.3</v>
+        <v>29.48</v>
       </c>
       <c r="H144" t="n">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J144" t="n">
-        <v>-49370</v>
+        <v>27793</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46148</v>
+        <v>46140</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -6236,77 +6236,77 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G145" t="n">
-        <v>233.5</v>
+        <v>211</v>
       </c>
       <c r="H145" t="n">
-        <v>332</v>
+        <v>602</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>1266</v>
       </c>
       <c r="J145" t="n">
-        <v>-233832</v>
+        <v>420132</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46148</v>
+        <v>46140</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>009816</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>5000</v>
+        <v>74</v>
       </c>
       <c r="G146" t="n">
-        <v>50.4</v>
+        <v>13.17</v>
       </c>
       <c r="H146" t="n">
-        <v>359</v>
+        <v>1</v>
       </c>
       <c r="I146" t="n">
-        <v>756</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>250885</v>
+        <v>-976</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46148</v>
+        <v>46140</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6320,33 +6320,33 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="G147" t="n">
-        <v>42.6</v>
+        <v>48.05</v>
       </c>
       <c r="H147" t="n">
-        <v>364</v>
+        <v>136</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>-255964</v>
+        <v>-96236</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46149</v>
+        <v>46140</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6360,33 +6360,33 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="G148" t="n">
-        <v>40.75</v>
+        <v>105</v>
       </c>
       <c r="H148" t="n">
-        <v>290</v>
+        <v>149</v>
       </c>
       <c r="I148" t="n">
-        <v>611</v>
+        <v>315</v>
       </c>
       <c r="J148" t="n">
-        <v>202849</v>
+        <v>104536</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46149</v>
+        <v>46146</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6400,33 +6400,33 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>103</v>
+        <v>1000</v>
       </c>
       <c r="G149" t="n">
-        <v>600</v>
+        <v>49.3</v>
       </c>
       <c r="H149" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="I149" t="n">
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>-61888</v>
+        <v>-49370</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -6436,37 +6436,37 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F150" t="n">
         <v>1000</v>
       </c>
       <c r="G150" t="n">
-        <v>40.9</v>
+        <v>233.5</v>
       </c>
       <c r="H150" t="n">
-        <v>58</v>
+        <v>332</v>
       </c>
       <c r="I150" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>40720</v>
+        <v>-233832</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6476,42 +6476,42 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="G151" t="n">
-        <v>256</v>
+        <v>50.4</v>
       </c>
       <c r="H151" t="n">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>756</v>
       </c>
       <c r="J151" t="n">
-        <v>-256364</v>
+        <v>250885</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46150</v>
+        <v>46148</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -6520,33 +6520,33 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>154</v>
+        <v>6000</v>
       </c>
       <c r="G152" t="n">
-        <v>32.48</v>
+        <v>42.6</v>
       </c>
       <c r="H152" t="n">
-        <v>20</v>
+        <v>364</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>-5022</v>
+        <v>-255964</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6560,38 +6560,38 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1000</v>
+        <v>103</v>
       </c>
       <c r="G153" t="n">
-        <v>51.1</v>
+        <v>600</v>
       </c>
       <c r="H153" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>-51172</v>
+        <v>-61888</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -6600,33 +6600,33 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="G154" t="n">
-        <v>124.7</v>
+        <v>256</v>
       </c>
       <c r="H154" t="n">
-        <v>20</v>
+        <v>364</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>-5008</v>
+        <v>-256364</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -6640,33 +6640,33 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="G155" t="n">
-        <v>47.2</v>
+        <v>40.9</v>
       </c>
       <c r="H155" t="n">
-        <v>605</v>
+        <v>58</v>
       </c>
       <c r="I155" t="n">
-        <v>1274</v>
+        <v>122</v>
       </c>
       <c r="J155" t="n">
-        <v>422921</v>
+        <v>40720</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -6676,82 +6676,82 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F156" t="n">
         <v>5000</v>
       </c>
       <c r="G156" t="n">
-        <v>59.8</v>
+        <v>40.75</v>
       </c>
       <c r="H156" t="n">
-        <v>426</v>
+        <v>290</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>611</v>
       </c>
       <c r="J156" t="n">
-        <v>-299426</v>
+        <v>202849</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46155</v>
+        <v>46150</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>5000</v>
+        <v>40</v>
       </c>
       <c r="G157" t="n">
-        <v>54.7</v>
+        <v>124.7</v>
       </c>
       <c r="H157" t="n">
-        <v>389</v>
+        <v>20</v>
       </c>
       <c r="I157" t="n">
-        <v>820</v>
+        <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>272291</v>
+        <v>-5008</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46157</v>
+        <v>46150</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6760,33 +6760,33 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>159</v>
+        <v>1000</v>
       </c>
       <c r="G158" t="n">
-        <v>31.5</v>
+        <v>51.1</v>
       </c>
       <c r="H158" t="n">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>-5028</v>
+        <v>-51172</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46157</v>
+        <v>46150</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -6800,33 +6800,33 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>39</v>
+        <v>154</v>
       </c>
       <c r="G159" t="n">
-        <v>129.3</v>
+        <v>32.48</v>
       </c>
       <c r="H159" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I159" t="n">
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>-5050</v>
+        <v>-5022</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>45971</v>
+        <v>46153</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -6836,37 +6836,37 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="G160" t="n">
-        <v>106</v>
+        <v>47.2</v>
       </c>
       <c r="H160" t="n">
-        <v>151</v>
+        <v>605</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>1274</v>
       </c>
       <c r="J160" t="n">
-        <v>-106151</v>
+        <v>422921</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>45973</v>
+        <v>46153</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -6880,33 +6880,33 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="G161" t="n">
-        <v>104.5</v>
+        <v>59.8</v>
       </c>
       <c r="H161" t="n">
-        <v>148</v>
+        <v>426</v>
       </c>
       <c r="I161" t="n">
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>-104648</v>
+        <v>-299426</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>45975</v>
+        <v>46155</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -6916,103 +6916,103 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="G162" t="n">
-        <v>101.5</v>
+        <v>54.7</v>
       </c>
       <c r="H162" t="n">
-        <v>144</v>
+        <v>389</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>820</v>
       </c>
       <c r="J162" t="n">
-        <v>-101644</v>
+        <v>272291</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46038</v>
+        <v>46157</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>2000</v>
+        <v>39</v>
       </c>
       <c r="G163" t="n">
-        <v>109</v>
+        <v>129.3</v>
       </c>
       <c r="H163" t="n">
-        <v>310</v>
+        <v>7</v>
       </c>
       <c r="I163" t="n">
-        <v>654</v>
+        <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>217036</v>
+        <v>-5050</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46085</v>
+        <v>46157</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>3000</v>
+        <v>159</v>
       </c>
       <c r="G164" t="n">
-        <v>163</v>
+        <v>31.5</v>
       </c>
       <c r="H164" t="n">
-        <v>696</v>
+        <v>20</v>
       </c>
       <c r="I164" t="n">
-        <v>1467</v>
+        <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>486837</v>
+        <v>-5028</v>
       </c>
     </row>
     <row r="165">
@@ -7217,16 +7217,16 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>009816</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7240,38 +7240,38 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="G170" t="n">
-        <v>36.85</v>
+        <v>15.26</v>
       </c>
       <c r="H170" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I170" t="n">
         <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>-5032</v>
+        <v>-978</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>主動統一台股增長</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>爸爸合資</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -7280,19 +7280,19 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>177</v>
+        <v>30</v>
       </c>
       <c r="G171" t="n">
-        <v>56.55</v>
+        <v>32.14</v>
       </c>
       <c r="H171" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I171" t="n">
         <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>-10029</v>
+        <v>-965</v>
       </c>
     </row>
     <row r="172">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -7320,38 +7320,38 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="G172" t="n">
-        <v>133.45</v>
+        <v>36.85</v>
       </c>
       <c r="H172" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>-5078</v>
+        <v>-5032</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>009816</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>爸爸合資</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -7360,33 +7360,33 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>64</v>
+        <v>177</v>
       </c>
       <c r="G173" t="n">
-        <v>15.26</v>
+        <v>56.55</v>
       </c>
       <c r="H173" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I173" t="n">
         <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>-978</v>
+        <v>-10029</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>主動統一台股增長</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -7400,19 +7400,139 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G174" t="n">
-        <v>32.14</v>
+        <v>133.45</v>
       </c>
       <c r="H174" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I174" t="n">
         <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>-965</v>
+        <v>-5078</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>譜瑞-KY</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>165</v>
+      </c>
+      <c r="G175" t="n">
+        <v>775</v>
+      </c>
+      <c r="H175" t="n">
+        <v>182</v>
+      </c>
+      <c r="I175" t="n">
+        <v>383</v>
+      </c>
+      <c r="J175" t="n">
+        <v>127310</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>譜瑞-KY</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>115</v>
+      </c>
+      <c r="G176" t="n">
+        <v>774</v>
+      </c>
+      <c r="H176" t="n">
+        <v>126</v>
+      </c>
+      <c r="I176" t="n">
+        <v>267</v>
+      </c>
+      <c r="J176" t="n">
+        <v>88617</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G177" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="H177" t="n">
+        <v>254</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>-179054</v>
       </c>
     </row>
   </sheetData>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J177"/>
+  <dimension ref="A1:J181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>009816</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>凱基台灣TOP50</t>
+          <t>主動統一台股增長</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4956,23 +4956,23 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>14000</v>
+        <v>283</v>
       </c>
       <c r="G113" t="n">
-        <v>10.8</v>
+        <v>20.83</v>
       </c>
       <c r="H113" t="n">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="I113" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>150834</v>
+        <v>-5915</v>
       </c>
     </row>
     <row r="114">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>009816</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>主動統一台股增長</t>
+          <t>凱基台灣TOP50</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5036,14 +5036,14 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>283</v>
+        <v>62</v>
       </c>
       <c r="G115" t="n">
-        <v>20.83</v>
+        <v>10.78</v>
       </c>
       <c r="H115" t="n">
         <v>20</v>
@@ -5052,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>-5915</v>
+        <v>648</v>
       </c>
     </row>
     <row r="116">
@@ -5120,19 +5120,19 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>62</v>
+        <v>14000</v>
       </c>
       <c r="G117" t="n">
-        <v>10.78</v>
+        <v>10.8</v>
       </c>
       <c r="H117" t="n">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="J117" t="n">
-        <v>648</v>
+        <v>150834</v>
       </c>
     </row>
     <row r="118">
@@ -6101,38 +6101,38 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>主動統一台股增長</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>獲利賣出</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>35</v>
+        <v>945</v>
       </c>
       <c r="G142" t="n">
-        <v>27.87</v>
+        <v>29.48</v>
       </c>
       <c r="H142" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J142" t="n">
-        <v>-976</v>
+        <v>27793</v>
       </c>
     </row>
     <row r="143">
@@ -6181,38 +6181,38 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>獲利賣出</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>945</v>
+        <v>2000</v>
       </c>
       <c r="G144" t="n">
-        <v>29.48</v>
+        <v>48.05</v>
       </c>
       <c r="H144" t="n">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="I144" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>27793</v>
+        <v>-96236</v>
       </c>
     </row>
     <row r="145">
@@ -6221,38 +6221,38 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>主動統一台股增長</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>2000</v>
+        <v>35</v>
       </c>
       <c r="G145" t="n">
-        <v>211</v>
+        <v>27.87</v>
       </c>
       <c r="H145" t="n">
-        <v>602</v>
+        <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>1266</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>420132</v>
+        <v>-976</v>
       </c>
     </row>
     <row r="146">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6316,23 +6316,23 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G147" t="n">
-        <v>48.05</v>
+        <v>105</v>
       </c>
       <c r="H147" t="n">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="J147" t="n">
-        <v>-96236</v>
+        <v>104536</v>
       </c>
     </row>
     <row r="148">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6360,19 +6360,19 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G148" t="n">
-        <v>105</v>
+        <v>211</v>
       </c>
       <c r="H148" t="n">
-        <v>149</v>
+        <v>602</v>
       </c>
       <c r="I148" t="n">
-        <v>315</v>
+        <v>1266</v>
       </c>
       <c r="J148" t="n">
-        <v>104536</v>
+        <v>420132</v>
       </c>
     </row>
     <row r="149">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6556,23 +6556,23 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>103</v>
+        <v>1000</v>
       </c>
       <c r="G153" t="n">
-        <v>600</v>
+        <v>40.9</v>
       </c>
       <c r="H153" t="n">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="J153" t="n">
-        <v>-61888</v>
+        <v>40720</v>
       </c>
     </row>
     <row r="154">
@@ -6581,12 +6581,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -6596,23 +6596,23 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>買</t>
+          <t>賣</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="G154" t="n">
-        <v>256</v>
+        <v>40.75</v>
       </c>
       <c r="H154" t="n">
-        <v>364</v>
+        <v>290</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>611</v>
       </c>
       <c r="J154" t="n">
-        <v>-256364</v>
+        <v>202849</v>
       </c>
     </row>
     <row r="155">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -6636,23 +6636,23 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1000</v>
+        <v>103</v>
       </c>
       <c r="G155" t="n">
-        <v>40.9</v>
+        <v>600</v>
       </c>
       <c r="H155" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="I155" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>40720</v>
+        <v>-61888</v>
       </c>
     </row>
     <row r="156">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -6676,23 +6676,23 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>賣</t>
+          <t>買</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="G156" t="n">
-        <v>40.75</v>
+        <v>256</v>
       </c>
       <c r="H156" t="n">
-        <v>290</v>
+        <v>364</v>
       </c>
       <c r="I156" t="n">
-        <v>611</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>202849</v>
+        <v>-256364</v>
       </c>
     </row>
     <row r="157">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>00757</t>
+          <t>00631L</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>元大台灣50正2</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="G157" t="n">
-        <v>124.7</v>
+        <v>32.48</v>
       </c>
       <c r="H157" t="n">
         <v>20</v>
@@ -6732,7 +6732,7 @@
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>-5008</v>
+        <v>-5022</v>
       </c>
     </row>
     <row r="158">
@@ -6741,17 +6741,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>00757</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>波段操作</t>
+          <t>定期定額</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6760,19 +6760,19 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="G158" t="n">
-        <v>51.1</v>
+        <v>124.7</v>
       </c>
       <c r="H158" t="n">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>-51172</v>
+        <v>-5008</v>
       </c>
     </row>
     <row r="159">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>00631L</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>元大台灣50正2</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>定期定額</t>
+          <t>波段操作</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -6800,19 +6800,19 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>154</v>
+        <v>1000</v>
       </c>
       <c r="G159" t="n">
-        <v>32.48</v>
+        <v>51.1</v>
       </c>
       <c r="H159" t="n">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="I159" t="n">
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>-5022</v>
+        <v>-51172</v>
       </c>
     </row>
     <row r="160">
@@ -7533,6 +7533,166 @@
       </c>
       <c r="J177" t="n">
         <v>-179054</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>00631L</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>元大台灣50正2</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>137</v>
+      </c>
+      <c r="G178" t="n">
+        <v>36.66</v>
+      </c>
+      <c r="H178" t="n">
+        <v>20</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>-5042</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G179" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="H179" t="n">
+        <v>117</v>
+      </c>
+      <c r="I179" t="n">
+        <v>247</v>
+      </c>
+      <c r="J179" t="n">
+        <v>82136</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>賣</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G180" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="H180" t="n">
+        <v>117</v>
+      </c>
+      <c r="I180" t="n">
+        <v>247</v>
+      </c>
+      <c r="J180" t="n">
+        <v>82036</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>00757</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>統一FANG+</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>定期定額</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>38</v>
+      </c>
+      <c r="G181" t="n">
+        <v>131.65</v>
+      </c>
+      <c r="H181" t="n">
+        <v>7</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>-5010</v>
       </c>
     </row>
   </sheetData>

--- a/股票紀錄.xlsx
+++ b/股票紀錄.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J181"/>
+  <dimension ref="A1:J182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7695,6 +7695,46 @@
         <v>-5010</v>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>波段操作</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>買</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G182" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="H182" t="n">
+        <v>384</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="n">
+        <v>-269884</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
